--- a/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7080400</v>
+        <v>7187000</v>
       </c>
       <c r="E8" s="3">
-        <v>6178500</v>
+        <v>6271500</v>
       </c>
       <c r="F8" s="3">
-        <v>5389000</v>
+        <v>5470200</v>
       </c>
       <c r="G8" s="3">
-        <v>6071900</v>
+        <v>6163300</v>
       </c>
       <c r="H8" s="3">
-        <v>6584200</v>
+        <v>6683300</v>
       </c>
       <c r="I8" s="3">
-        <v>6423100</v>
+        <v>6519800</v>
       </c>
       <c r="J8" s="3">
-        <v>5599800</v>
+        <v>5684100</v>
       </c>
       <c r="K8" s="3">
         <v>6430400</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6039900</v>
+        <v>6130900</v>
       </c>
       <c r="E9" s="3">
-        <v>5257600</v>
+        <v>5336800</v>
       </c>
       <c r="F9" s="3">
-        <v>4530400</v>
+        <v>4598600</v>
       </c>
       <c r="G9" s="3">
-        <v>5074300</v>
+        <v>5150700</v>
       </c>
       <c r="H9" s="3">
-        <v>5474600</v>
+        <v>5557000</v>
       </c>
       <c r="I9" s="3">
-        <v>5321400</v>
+        <v>5401500</v>
       </c>
       <c r="J9" s="3">
-        <v>4576000</v>
+        <v>4644900</v>
       </c>
       <c r="K9" s="3">
         <v>5394500</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1040500</v>
+        <v>1056200</v>
       </c>
       <c r="E10" s="3">
-        <v>920900</v>
+        <v>934800</v>
       </c>
       <c r="F10" s="3">
-        <v>858600</v>
+        <v>871600</v>
       </c>
       <c r="G10" s="3">
-        <v>997600</v>
+        <v>1012600</v>
       </c>
       <c r="H10" s="3">
-        <v>1109600</v>
+        <v>1126300</v>
       </c>
       <c r="I10" s="3">
-        <v>1101700</v>
+        <v>1118300</v>
       </c>
       <c r="J10" s="3">
-        <v>1023800</v>
+        <v>1039200</v>
       </c>
       <c r="K10" s="3">
         <v>1035900</v>
@@ -867,22 +867,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>128200</v>
+        <v>130100</v>
       </c>
       <c r="E12" s="3">
-        <v>114300</v>
+        <v>116000</v>
       </c>
       <c r="F12" s="3">
-        <v>108500</v>
+        <v>110100</v>
       </c>
       <c r="G12" s="3">
-        <v>114100</v>
+        <v>115800</v>
       </c>
       <c r="H12" s="3">
-        <v>114600</v>
+        <v>116300</v>
       </c>
       <c r="I12" s="3">
-        <v>102900</v>
+        <v>104500</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -951,25 +951,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>30500</v>
+        <v>30900</v>
       </c>
       <c r="E14" s="3">
-        <v>11700</v>
+        <v>11900</v>
       </c>
       <c r="F14" s="3">
-        <v>69500</v>
+        <v>70500</v>
       </c>
       <c r="G14" s="3">
-        <v>30300</v>
+        <v>30800</v>
       </c>
       <c r="H14" s="3">
-        <v>61600</v>
+        <v>62500</v>
       </c>
       <c r="I14" s="3">
-        <v>98500</v>
+        <v>100000</v>
       </c>
       <c r="J14" s="3">
-        <v>89800</v>
+        <v>91200</v>
       </c>
       <c r="K14" s="3">
         <v>131500</v>
@@ -993,22 +993,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>34300</v>
+        <v>34900</v>
       </c>
       <c r="E15" s="3">
-        <v>25000</v>
+        <v>25400</v>
       </c>
       <c r="F15" s="3">
-        <v>28600</v>
+        <v>29000</v>
       </c>
       <c r="G15" s="3">
-        <v>22300</v>
+        <v>22700</v>
       </c>
       <c r="H15" s="3">
-        <v>17700</v>
+        <v>18000</v>
       </c>
       <c r="I15" s="3">
-        <v>17200</v>
+        <v>17400</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>8</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7008300</v>
+        <v>7113900</v>
       </c>
       <c r="E17" s="3">
-        <v>6114300</v>
+        <v>6206400</v>
       </c>
       <c r="F17" s="3">
-        <v>5402500</v>
+        <v>5483900</v>
       </c>
       <c r="G17" s="3">
-        <v>5945700</v>
+        <v>6035200</v>
       </c>
       <c r="H17" s="3">
-        <v>6374500</v>
+        <v>6470500</v>
       </c>
       <c r="I17" s="3">
-        <v>6224100</v>
+        <v>6317900</v>
       </c>
       <c r="J17" s="3">
-        <v>5433200</v>
+        <v>5515000</v>
       </c>
       <c r="K17" s="3">
         <v>6362500</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>72100</v>
+        <v>73200</v>
       </c>
       <c r="E18" s="3">
-        <v>64200</v>
+        <v>65200</v>
       </c>
       <c r="F18" s="3">
-        <v>-13500</v>
+        <v>-13700</v>
       </c>
       <c r="G18" s="3">
-        <v>126200</v>
+        <v>128100</v>
       </c>
       <c r="H18" s="3">
-        <v>209600</v>
+        <v>212800</v>
       </c>
       <c r="I18" s="3">
-        <v>199000</v>
+        <v>202000</v>
       </c>
       <c r="J18" s="3">
-        <v>166600</v>
+        <v>169100</v>
       </c>
       <c r="K18" s="3">
         <v>67800</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>171200</v>
+        <v>173800</v>
       </c>
       <c r="E20" s="3">
-        <v>93900</v>
+        <v>95300</v>
       </c>
       <c r="F20" s="3">
-        <v>178900</v>
+        <v>181600</v>
       </c>
       <c r="G20" s="3">
-        <v>106700</v>
+        <v>108300</v>
       </c>
       <c r="H20" s="3">
-        <v>54900</v>
+        <v>55700</v>
       </c>
       <c r="I20" s="3">
-        <v>96100</v>
+        <v>97600</v>
       </c>
       <c r="J20" s="3">
-        <v>42200</v>
+        <v>42800</v>
       </c>
       <c r="K20" s="3">
         <v>116600</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>501700</v>
+        <v>511600</v>
       </c>
       <c r="E21" s="3">
-        <v>381000</v>
+        <v>388700</v>
       </c>
       <c r="F21" s="3">
-        <v>377900</v>
+        <v>385600</v>
       </c>
       <c r="G21" s="3">
-        <v>427400</v>
+        <v>435600</v>
       </c>
       <c r="H21" s="3">
-        <v>438100</v>
+        <v>446300</v>
       </c>
       <c r="I21" s="3">
-        <v>461100</v>
+        <v>469500</v>
       </c>
       <c r="J21" s="3">
-        <v>363300</v>
+        <v>370200</v>
       </c>
       <c r="K21" s="3">
         <v>353600</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>42100</v>
+        <v>42700</v>
       </c>
       <c r="E22" s="3">
-        <v>22400</v>
+        <v>22700</v>
       </c>
       <c r="F22" s="3">
-        <v>23800</v>
+        <v>24200</v>
       </c>
       <c r="G22" s="3">
-        <v>28700</v>
+        <v>29200</v>
       </c>
       <c r="H22" s="3">
-        <v>27100</v>
+        <v>27500</v>
       </c>
       <c r="I22" s="3">
-        <v>26400</v>
+        <v>26800</v>
       </c>
       <c r="J22" s="3">
-        <v>23100</v>
+        <v>23500</v>
       </c>
       <c r="K22" s="3">
         <v>27300</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>201200</v>
+        <v>204200</v>
       </c>
       <c r="E23" s="3">
-        <v>135700</v>
+        <v>137700</v>
       </c>
       <c r="F23" s="3">
-        <v>141500</v>
+        <v>143700</v>
       </c>
       <c r="G23" s="3">
-        <v>204200</v>
+        <v>207300</v>
       </c>
       <c r="H23" s="3">
-        <v>237400</v>
+        <v>241000</v>
       </c>
       <c r="I23" s="3">
-        <v>268700</v>
+        <v>272700</v>
       </c>
       <c r="J23" s="3">
-        <v>185700</v>
+        <v>188500</v>
       </c>
       <c r="K23" s="3">
         <v>157100</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>70700</v>
+        <v>71800</v>
       </c>
       <c r="E24" s="3">
-        <v>47700</v>
+        <v>48500</v>
       </c>
       <c r="F24" s="3">
-        <v>61200</v>
+        <v>62100</v>
       </c>
       <c r="G24" s="3">
-        <v>78000</v>
+        <v>79200</v>
       </c>
       <c r="H24" s="3">
-        <v>22000</v>
+        <v>22300</v>
       </c>
       <c r="I24" s="3">
-        <v>54100</v>
+        <v>54900</v>
       </c>
       <c r="J24" s="3">
-        <v>36700</v>
+        <v>37300</v>
       </c>
       <c r="K24" s="3">
         <v>58400</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>130500</v>
+        <v>132400</v>
       </c>
       <c r="E26" s="3">
-        <v>87900</v>
+        <v>89200</v>
       </c>
       <c r="F26" s="3">
-        <v>80300</v>
+        <v>81500</v>
       </c>
       <c r="G26" s="3">
-        <v>126100</v>
+        <v>128000</v>
       </c>
       <c r="H26" s="3">
-        <v>215400</v>
+        <v>218700</v>
       </c>
       <c r="I26" s="3">
-        <v>214600</v>
+        <v>217800</v>
       </c>
       <c r="J26" s="3">
-        <v>148900</v>
+        <v>151200</v>
       </c>
       <c r="K26" s="3">
         <v>98800</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>67400</v>
+      </c>
+      <c r="G27" s="3">
         <v>118900</v>
       </c>
-      <c r="E27" s="3">
-        <v>67000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>66400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>117100</v>
-      </c>
       <c r="H27" s="3">
-        <v>193300</v>
+        <v>196200</v>
       </c>
       <c r="I27" s="3">
-        <v>189600</v>
+        <v>192400</v>
       </c>
       <c r="J27" s="3">
-        <v>116700</v>
+        <v>118400</v>
       </c>
       <c r="K27" s="3">
         <v>73600</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-171200</v>
+        <v>-173800</v>
       </c>
       <c r="E32" s="3">
-        <v>-93900</v>
+        <v>-95300</v>
       </c>
       <c r="F32" s="3">
-        <v>-178900</v>
+        <v>-181600</v>
       </c>
       <c r="G32" s="3">
-        <v>-106700</v>
+        <v>-108300</v>
       </c>
       <c r="H32" s="3">
-        <v>-54900</v>
+        <v>-55700</v>
       </c>
       <c r="I32" s="3">
-        <v>-96100</v>
+        <v>-97600</v>
       </c>
       <c r="J32" s="3">
-        <v>-42200</v>
+        <v>-42800</v>
       </c>
       <c r="K32" s="3">
         <v>-116600</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>67400</v>
+      </c>
+      <c r="G33" s="3">
         <v>118900</v>
       </c>
-      <c r="E33" s="3">
-        <v>67000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>66400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>117100</v>
-      </c>
       <c r="H33" s="3">
-        <v>193300</v>
+        <v>196200</v>
       </c>
       <c r="I33" s="3">
-        <v>189600</v>
+        <v>192400</v>
       </c>
       <c r="J33" s="3">
-        <v>116700</v>
+        <v>118400</v>
       </c>
       <c r="K33" s="3">
         <v>73600</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>67400</v>
+      </c>
+      <c r="G35" s="3">
         <v>118900</v>
       </c>
-      <c r="E35" s="3">
-        <v>67000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>66400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>117100</v>
-      </c>
       <c r="H35" s="3">
-        <v>193300</v>
+        <v>196200</v>
       </c>
       <c r="I35" s="3">
-        <v>189600</v>
+        <v>192400</v>
       </c>
       <c r="J35" s="3">
-        <v>116700</v>
+        <v>118400</v>
       </c>
       <c r="K35" s="3">
         <v>73600</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>314900</v>
+        <v>319700</v>
       </c>
       <c r="E41" s="3">
-        <v>432600</v>
+        <v>439100</v>
       </c>
       <c r="F41" s="3">
-        <v>560200</v>
+        <v>568600</v>
       </c>
       <c r="G41" s="3">
-        <v>360900</v>
+        <v>366400</v>
       </c>
       <c r="H41" s="3">
-        <v>296300</v>
+        <v>300800</v>
       </c>
       <c r="I41" s="3">
-        <v>336200</v>
+        <v>341300</v>
       </c>
       <c r="J41" s="3">
-        <v>313200</v>
+        <v>317900</v>
       </c>
       <c r="K41" s="3">
         <v>385900</v>
@@ -1949,19 +1949,19 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>34000</v>
+        <v>34600</v>
       </c>
       <c r="E42" s="3">
-        <v>21600</v>
+        <v>22000</v>
       </c>
       <c r="F42" s="3">
-        <v>19400</v>
+        <v>19700</v>
       </c>
       <c r="G42" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="H42" s="3">
-        <v>15700</v>
+        <v>16000</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1515000</v>
+        <v>1537800</v>
       </c>
       <c r="E43" s="3">
-        <v>1522400</v>
+        <v>1545300</v>
       </c>
       <c r="F43" s="3">
-        <v>1268500</v>
+        <v>1287600</v>
       </c>
       <c r="G43" s="3">
-        <v>1270000</v>
+        <v>1289100</v>
       </c>
       <c r="H43" s="3">
-        <v>1449200</v>
+        <v>1471100</v>
       </c>
       <c r="I43" s="3">
-        <v>1481500</v>
+        <v>1503800</v>
       </c>
       <c r="J43" s="3">
-        <v>1312300</v>
+        <v>1332000</v>
       </c>
       <c r="K43" s="3">
         <v>1364300</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1144000</v>
+        <v>1161300</v>
       </c>
       <c r="E44" s="3">
-        <v>1089700</v>
+        <v>1106100</v>
       </c>
       <c r="F44" s="3">
-        <v>802400</v>
+        <v>814400</v>
       </c>
       <c r="G44" s="3">
-        <v>769300</v>
+        <v>780900</v>
       </c>
       <c r="H44" s="3">
-        <v>816000</v>
+        <v>828300</v>
       </c>
       <c r="I44" s="3">
-        <v>755600</v>
+        <v>766900</v>
       </c>
       <c r="J44" s="3">
-        <v>692900</v>
+        <v>703300</v>
       </c>
       <c r="K44" s="3">
         <v>684800</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>224500</v>
+        <v>227800</v>
       </c>
       <c r="E45" s="3">
-        <v>273300</v>
+        <v>277400</v>
       </c>
       <c r="F45" s="3">
-        <v>203500</v>
+        <v>206600</v>
       </c>
       <c r="G45" s="3">
-        <v>158100</v>
+        <v>160400</v>
       </c>
       <c r="H45" s="3">
-        <v>214900</v>
+        <v>218200</v>
       </c>
       <c r="I45" s="3">
-        <v>256200</v>
+        <v>260000</v>
       </c>
       <c r="J45" s="3">
-        <v>220400</v>
+        <v>223700</v>
       </c>
       <c r="K45" s="3">
         <v>240600</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3232500</v>
+        <v>3281200</v>
       </c>
       <c r="E46" s="3">
-        <v>3339700</v>
+        <v>3390000</v>
       </c>
       <c r="F46" s="3">
-        <v>2854000</v>
+        <v>2896900</v>
       </c>
       <c r="G46" s="3">
-        <v>2564200</v>
+        <v>2602800</v>
       </c>
       <c r="H46" s="3">
-        <v>2792200</v>
+        <v>2834300</v>
       </c>
       <c r="I46" s="3">
-        <v>2763500</v>
+        <v>2805100</v>
       </c>
       <c r="J46" s="3">
-        <v>2539100</v>
+        <v>2577400</v>
       </c>
       <c r="K46" s="3">
         <v>2675600</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1619000</v>
+        <v>1643300</v>
       </c>
       <c r="E47" s="3">
-        <v>809700</v>
+        <v>821900</v>
       </c>
       <c r="F47" s="3">
-        <v>728000</v>
+        <v>739000</v>
       </c>
       <c r="G47" s="3">
-        <v>706100</v>
+        <v>716700</v>
       </c>
       <c r="H47" s="3">
-        <v>824800</v>
+        <v>837200</v>
       </c>
       <c r="I47" s="3">
-        <v>910500</v>
+        <v>924200</v>
       </c>
       <c r="J47" s="3">
-        <v>870200</v>
+        <v>883300</v>
       </c>
       <c r="K47" s="3">
         <v>832500</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2102400</v>
+        <v>2134100</v>
       </c>
       <c r="E48" s="3">
-        <v>1727500</v>
+        <v>1753500</v>
       </c>
       <c r="F48" s="3">
-        <v>1638400</v>
+        <v>1663100</v>
       </c>
       <c r="G48" s="3">
-        <v>1688000</v>
+        <v>1713400</v>
       </c>
       <c r="H48" s="3">
-        <v>1523000</v>
+        <v>1545900</v>
       </c>
       <c r="I48" s="3">
-        <v>1600400</v>
+        <v>1624500</v>
       </c>
       <c r="J48" s="3">
-        <v>1364500</v>
+        <v>1385000</v>
       </c>
       <c r="K48" s="3">
         <v>1444600</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>134400</v>
+        <v>136400</v>
       </c>
       <c r="E49" s="3">
-        <v>136300</v>
+        <v>138300</v>
       </c>
       <c r="F49" s="3">
-        <v>134500</v>
+        <v>136500</v>
       </c>
       <c r="G49" s="3">
-        <v>106900</v>
+        <v>108500</v>
       </c>
       <c r="H49" s="3">
-        <v>81000</v>
+        <v>82300</v>
       </c>
       <c r="I49" s="3">
-        <v>75100</v>
+        <v>76200</v>
       </c>
       <c r="J49" s="3">
-        <v>64700</v>
+        <v>65700</v>
       </c>
       <c r="K49" s="3">
         <v>62600</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>255600</v>
+        <v>259400</v>
       </c>
       <c r="E52" s="3">
-        <v>201100</v>
+        <v>204200</v>
       </c>
       <c r="F52" s="3">
-        <v>170000</v>
+        <v>172500</v>
       </c>
       <c r="G52" s="3">
-        <v>211100</v>
+        <v>214300</v>
       </c>
       <c r="H52" s="3">
-        <v>210700</v>
+        <v>213900</v>
       </c>
       <c r="I52" s="3">
-        <v>221400</v>
+        <v>224800</v>
       </c>
       <c r="J52" s="3">
-        <v>142400</v>
+        <v>144500</v>
       </c>
       <c r="K52" s="3">
         <v>171700</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6198200</v>
+        <v>6291600</v>
       </c>
       <c r="E54" s="3">
-        <v>6214200</v>
+        <v>6307800</v>
       </c>
       <c r="F54" s="3">
-        <v>5524800</v>
+        <v>5608000</v>
       </c>
       <c r="G54" s="3">
-        <v>5276300</v>
+        <v>5355700</v>
       </c>
       <c r="H54" s="3">
-        <v>5431700</v>
+        <v>5513500</v>
       </c>
       <c r="I54" s="3">
-        <v>5369300</v>
+        <v>5450200</v>
       </c>
       <c r="J54" s="3">
-        <v>4980800</v>
+        <v>5055800</v>
       </c>
       <c r="K54" s="3">
         <v>5187100</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>832700</v>
+        <v>845300</v>
       </c>
       <c r="E57" s="3">
-        <v>849800</v>
+        <v>862600</v>
       </c>
       <c r="F57" s="3">
-        <v>766900</v>
+        <v>778500</v>
       </c>
       <c r="G57" s="3">
-        <v>740900</v>
+        <v>752100</v>
       </c>
       <c r="H57" s="3">
-        <v>872600</v>
+        <v>885800</v>
       </c>
       <c r="I57" s="3">
-        <v>825900</v>
+        <v>838400</v>
       </c>
       <c r="J57" s="3">
-        <v>717700</v>
+        <v>728500</v>
       </c>
       <c r="K57" s="3">
         <v>737900</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2079700</v>
+        <v>2111000</v>
       </c>
       <c r="E58" s="3">
-        <v>1132500</v>
+        <v>1149500</v>
       </c>
       <c r="F58" s="3">
-        <v>896600</v>
+        <v>910100</v>
       </c>
       <c r="G58" s="3">
-        <v>843800</v>
+        <v>856500</v>
       </c>
       <c r="H58" s="3">
-        <v>708600</v>
+        <v>719200</v>
       </c>
       <c r="I58" s="3">
-        <v>772100</v>
+        <v>783700</v>
       </c>
       <c r="J58" s="3">
-        <v>666100</v>
+        <v>676100</v>
       </c>
       <c r="K58" s="3">
         <v>910000</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1082700</v>
+        <v>1099000</v>
       </c>
       <c r="E59" s="3">
-        <v>539000</v>
+        <v>547100</v>
       </c>
       <c r="F59" s="3">
-        <v>429400</v>
+        <v>435800</v>
       </c>
       <c r="G59" s="3">
-        <v>537700</v>
+        <v>545800</v>
       </c>
       <c r="H59" s="3">
-        <v>620800</v>
+        <v>630100</v>
       </c>
       <c r="I59" s="3">
-        <v>595400</v>
+        <v>604400</v>
       </c>
       <c r="J59" s="3">
-        <v>564200</v>
+        <v>572700</v>
       </c>
       <c r="K59" s="3">
         <v>552200</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2530000</v>
+        <v>2568100</v>
       </c>
       <c r="E60" s="3">
-        <v>2521300</v>
+        <v>2559300</v>
       </c>
       <c r="F60" s="3">
-        <v>2093000</v>
+        <v>2124500</v>
       </c>
       <c r="G60" s="3">
-        <v>2122500</v>
+        <v>2154400</v>
       </c>
       <c r="H60" s="3">
-        <v>2202000</v>
+        <v>2235100</v>
       </c>
       <c r="I60" s="3">
-        <v>2193400</v>
+        <v>2226500</v>
       </c>
       <c r="J60" s="3">
-        <v>1947900</v>
+        <v>1977300</v>
       </c>
       <c r="K60" s="3">
         <v>2200200</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1026200</v>
+        <v>1041600</v>
       </c>
       <c r="E61" s="3">
-        <v>1199900</v>
+        <v>1218000</v>
       </c>
       <c r="F61" s="3">
-        <v>1083600</v>
+        <v>1099900</v>
       </c>
       <c r="G61" s="3">
-        <v>876700</v>
+        <v>889900</v>
       </c>
       <c r="H61" s="3">
-        <v>924900</v>
+        <v>938900</v>
       </c>
       <c r="I61" s="3">
-        <v>944400</v>
+        <v>958600</v>
       </c>
       <c r="J61" s="3">
-        <v>1010800</v>
+        <v>1026100</v>
       </c>
       <c r="K61" s="3">
         <v>1005500</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>500800</v>
+        <v>508300</v>
       </c>
       <c r="E62" s="3">
-        <v>407600</v>
+        <v>413700</v>
       </c>
       <c r="F62" s="3">
-        <v>411900</v>
+        <v>418100</v>
       </c>
       <c r="G62" s="3">
-        <v>464200</v>
+        <v>471200</v>
       </c>
       <c r="H62" s="3">
-        <v>446100</v>
+        <v>452900</v>
       </c>
       <c r="I62" s="3">
-        <v>488100</v>
+        <v>495500</v>
       </c>
       <c r="J62" s="3">
-        <v>448000</v>
+        <v>454800</v>
       </c>
       <c r="K62" s="3">
         <v>521800</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4195300</v>
+        <v>4258400</v>
       </c>
       <c r="E66" s="3">
-        <v>4360200</v>
+        <v>4425900</v>
       </c>
       <c r="F66" s="3">
-        <v>3799200</v>
+        <v>3856500</v>
       </c>
       <c r="G66" s="3">
-        <v>3680800</v>
+        <v>3736200</v>
       </c>
       <c r="H66" s="3">
-        <v>3787200</v>
+        <v>3844200</v>
       </c>
       <c r="I66" s="3">
-        <v>3798800</v>
+        <v>3856000</v>
       </c>
       <c r="J66" s="3">
-        <v>3608300</v>
+        <v>3662600</v>
       </c>
       <c r="K66" s="3">
         <v>3914300</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1273300</v>
+        <v>1292500</v>
       </c>
       <c r="E72" s="3">
-        <v>1157700</v>
+        <v>1175100</v>
       </c>
       <c r="F72" s="3">
-        <v>1119100</v>
+        <v>1136000</v>
       </c>
       <c r="G72" s="3">
-        <v>1096300</v>
+        <v>1112800</v>
       </c>
       <c r="H72" s="3">
-        <v>1007600</v>
+        <v>1022800</v>
       </c>
       <c r="I72" s="3">
-        <v>850800</v>
+        <v>863600</v>
       </c>
       <c r="J72" s="3">
-        <v>690200</v>
+        <v>700600</v>
       </c>
       <c r="K72" s="3">
         <v>663800</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2003000</v>
+        <v>2033100</v>
       </c>
       <c r="E76" s="3">
-        <v>1854000</v>
+        <v>1881900</v>
       </c>
       <c r="F76" s="3">
-        <v>1725500</v>
+        <v>1751500</v>
       </c>
       <c r="G76" s="3">
-        <v>1595500</v>
+        <v>1619500</v>
       </c>
       <c r="H76" s="3">
-        <v>1644500</v>
+        <v>1669200</v>
       </c>
       <c r="I76" s="3">
-        <v>1570500</v>
+        <v>1594100</v>
       </c>
       <c r="J76" s="3">
-        <v>1372600</v>
+        <v>1393200</v>
       </c>
       <c r="K76" s="3">
         <v>1272700</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>67400</v>
+      </c>
+      <c r="G81" s="3">
         <v>118900</v>
       </c>
-      <c r="E81" s="3">
-        <v>67000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>66400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>117100</v>
-      </c>
       <c r="H81" s="3">
-        <v>193300</v>
+        <v>196200</v>
       </c>
       <c r="I81" s="3">
-        <v>189600</v>
+        <v>192400</v>
       </c>
       <c r="J81" s="3">
-        <v>116700</v>
+        <v>118400</v>
       </c>
       <c r="K81" s="3">
         <v>73600</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>259600</v>
+        <v>263500</v>
       </c>
       <c r="E83" s="3">
-        <v>223900</v>
+        <v>227300</v>
       </c>
       <c r="F83" s="3">
-        <v>213600</v>
+        <v>216800</v>
       </c>
       <c r="G83" s="3">
-        <v>195400</v>
+        <v>198300</v>
       </c>
       <c r="H83" s="3">
-        <v>174400</v>
+        <v>177100</v>
       </c>
       <c r="I83" s="3">
-        <v>166700</v>
+        <v>169200</v>
       </c>
       <c r="J83" s="3">
-        <v>155200</v>
+        <v>157500</v>
       </c>
       <c r="K83" s="3">
         <v>170800</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>250500</v>
+        <v>254200</v>
       </c>
       <c r="E89" s="3">
-        <v>-84200</v>
+        <v>-85500</v>
       </c>
       <c r="F89" s="3">
-        <v>-3300</v>
+        <v>-3400</v>
       </c>
       <c r="G89" s="3">
-        <v>281800</v>
+        <v>286000</v>
       </c>
       <c r="H89" s="3">
-        <v>310000</v>
+        <v>314600</v>
       </c>
       <c r="I89" s="3">
-        <v>257900</v>
+        <v>261700</v>
       </c>
       <c r="J89" s="3">
-        <v>275800</v>
+        <v>280000</v>
       </c>
       <c r="K89" s="3">
         <v>313000</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-238200</v>
+        <v>-241800</v>
       </c>
       <c r="E91" s="3">
-        <v>-242300</v>
+        <v>-246000</v>
       </c>
       <c r="F91" s="3">
-        <v>-221700</v>
+        <v>-225000</v>
       </c>
       <c r="G91" s="3">
-        <v>-314200</v>
+        <v>-318900</v>
       </c>
       <c r="H91" s="3">
-        <v>-285900</v>
+        <v>-290200</v>
       </c>
       <c r="I91" s="3">
-        <v>-228100</v>
+        <v>-231500</v>
       </c>
       <c r="J91" s="3">
-        <v>-188900</v>
+        <v>-191700</v>
       </c>
       <c r="K91" s="3">
         <v>-188500</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-143900</v>
+        <v>-146100</v>
       </c>
       <c r="E94" s="3">
-        <v>-266100</v>
+        <v>-270100</v>
       </c>
       <c r="F94" s="3">
-        <v>-12700</v>
+        <v>-12900</v>
       </c>
       <c r="G94" s="3">
-        <v>-219900</v>
+        <v>-223200</v>
       </c>
       <c r="H94" s="3">
-        <v>-206100</v>
+        <v>-209200</v>
       </c>
       <c r="I94" s="3">
-        <v>-227900</v>
+        <v>-231300</v>
       </c>
       <c r="J94" s="3">
-        <v>-241400</v>
+        <v>-245100</v>
       </c>
       <c r="K94" s="3">
         <v>14300</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-28100</v>
+        <v>-28500</v>
       </c>
       <c r="E96" s="3">
-        <v>-28200</v>
+        <v>-28600</v>
       </c>
       <c r="F96" s="3">
-        <v>-39800</v>
+        <v>-40400</v>
       </c>
       <c r="G96" s="3">
-        <v>-39800</v>
+        <v>-40400</v>
       </c>
       <c r="H96" s="3">
-        <v>-37500</v>
+        <v>-38100</v>
       </c>
       <c r="I96" s="3">
-        <v>-25800</v>
+        <v>-26200</v>
       </c>
       <c r="J96" s="3">
-        <v>-18700</v>
+        <v>-19000</v>
       </c>
       <c r="K96" s="3">
         <v>-15500</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-228900</v>
+        <v>-232400</v>
       </c>
       <c r="E100" s="3">
-        <v>232500</v>
+        <v>236000</v>
       </c>
       <c r="F100" s="3">
-        <v>233300</v>
+        <v>236800</v>
       </c>
       <c r="G100" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="H100" s="3">
-        <v>-128900</v>
+        <v>-130900</v>
       </c>
       <c r="I100" s="3">
-        <v>-12900</v>
+        <v>-13100</v>
       </c>
       <c r="J100" s="3">
-        <v>-68900</v>
+        <v>-69900</v>
       </c>
       <c r="K100" s="3">
         <v>-153900</v>
@@ -4204,22 +4204,22 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>18300</v>
+        <v>18500</v>
       </c>
       <c r="E101" s="3">
-        <v>-12100</v>
+        <v>-12200</v>
       </c>
       <c r="F101" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="G101" s="3">
-        <v>-6200</v>
+        <v>-6300</v>
       </c>
       <c r="H101" s="3">
         <v>5700</v>
       </c>
       <c r="I101" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="J101" s="3">
         <v>-2100</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-104100</v>
+        <v>-105700</v>
       </c>
       <c r="E102" s="3">
-        <v>-129900</v>
+        <v>-131800</v>
       </c>
       <c r="F102" s="3">
-        <v>213400</v>
+        <v>216600</v>
       </c>
       <c r="G102" s="3">
-        <v>54600</v>
+        <v>55400</v>
       </c>
       <c r="H102" s="3">
-        <v>-19400</v>
+        <v>-19700</v>
       </c>
       <c r="I102" s="3">
-        <v>24000</v>
+        <v>24300</v>
       </c>
       <c r="J102" s="3">
-        <v>-36600</v>
+        <v>-37100</v>
       </c>
       <c r="K102" s="3">
         <v>163000</v>

--- a/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7187000</v>
+        <v>6740600</v>
       </c>
       <c r="E8" s="3">
-        <v>6271500</v>
+        <v>6803200</v>
       </c>
       <c r="F8" s="3">
-        <v>5470200</v>
+        <v>5936600</v>
       </c>
       <c r="G8" s="3">
-        <v>6163300</v>
+        <v>5178000</v>
       </c>
       <c r="H8" s="3">
-        <v>6683300</v>
+        <v>5834100</v>
       </c>
       <c r="I8" s="3">
-        <v>6519800</v>
+        <v>6326300</v>
       </c>
       <c r="J8" s="3">
+        <v>6171600</v>
+      </c>
+      <c r="K8" s="3">
         <v>5684100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6430400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7402500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8535100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8405700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8306000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6130900</v>
+        <v>5726300</v>
       </c>
       <c r="E9" s="3">
-        <v>5336800</v>
+        <v>11606800</v>
       </c>
       <c r="F9" s="3">
-        <v>4598600</v>
+        <v>5051700</v>
       </c>
       <c r="G9" s="3">
-        <v>5150700</v>
+        <v>4353000</v>
       </c>
       <c r="H9" s="3">
-        <v>5557000</v>
+        <v>4875600</v>
       </c>
       <c r="I9" s="3">
-        <v>5401500</v>
+        <v>5260200</v>
       </c>
       <c r="J9" s="3">
+        <v>5113000</v>
+      </c>
+      <c r="K9" s="3">
         <v>4644900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5394500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6347100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7276800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7152200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7114000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1056200</v>
+        <v>1014400</v>
       </c>
       <c r="E10" s="3">
-        <v>934800</v>
+        <v>-4803600</v>
       </c>
       <c r="F10" s="3">
-        <v>871600</v>
+        <v>884900</v>
       </c>
       <c r="G10" s="3">
-        <v>1012600</v>
+        <v>825000</v>
       </c>
       <c r="H10" s="3">
-        <v>1126300</v>
+        <v>958500</v>
       </c>
       <c r="I10" s="3">
-        <v>1118300</v>
+        <v>1066200</v>
       </c>
       <c r="J10" s="3">
+        <v>1058600</v>
+      </c>
+      <c r="K10" s="3">
         <v>1039200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1035900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1055300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1258300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1253400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1192000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>130100</v>
+      <c r="D12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E12" s="3">
-        <v>116000</v>
+        <v>123200</v>
       </c>
       <c r="F12" s="3">
+        <v>109800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>104200</v>
+      </c>
+      <c r="H12" s="3">
+        <v>109600</v>
+      </c>
+      <c r="I12" s="3">
         <v>110100</v>
       </c>
-      <c r="G12" s="3">
-        <v>115800</v>
-      </c>
-      <c r="H12" s="3">
-        <v>116300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>104500</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>98900</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>119300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>130100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>148600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>133600</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,74 +960,80 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>30900</v>
+        <v>3900</v>
       </c>
       <c r="E14" s="3">
-        <v>11900</v>
+        <v>55000</v>
       </c>
       <c r="F14" s="3">
-        <v>70500</v>
+        <v>11200</v>
       </c>
       <c r="G14" s="3">
-        <v>30800</v>
+        <v>66800</v>
       </c>
       <c r="H14" s="3">
-        <v>62500</v>
+        <v>29100</v>
       </c>
       <c r="I14" s="3">
-        <v>100000</v>
+        <v>59200</v>
       </c>
       <c r="J14" s="3">
+        <v>94700</v>
+      </c>
+      <c r="K14" s="3">
         <v>91200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>131500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>82200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>115400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>37400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>212800</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>34900</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E15" s="3">
-        <v>25400</v>
+        <v>33000</v>
       </c>
       <c r="F15" s="3">
-        <v>29000</v>
+        <v>24100</v>
       </c>
       <c r="G15" s="3">
-        <v>22700</v>
+        <v>27400</v>
       </c>
       <c r="H15" s="3">
-        <v>18000</v>
+        <v>21400</v>
       </c>
       <c r="I15" s="3">
-        <v>17400</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
+        <v>17000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>16500</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -1022,15 +1044,18 @@
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="3">
         <v>36500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>31600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7113900</v>
+        <v>6673300</v>
       </c>
       <c r="E17" s="3">
-        <v>6206400</v>
+        <v>6733900</v>
       </c>
       <c r="F17" s="3">
-        <v>5483900</v>
+        <v>5874900</v>
       </c>
       <c r="G17" s="3">
-        <v>6035200</v>
+        <v>5191000</v>
       </c>
       <c r="H17" s="3">
-        <v>6470500</v>
+        <v>5712900</v>
       </c>
       <c r="I17" s="3">
-        <v>6317900</v>
+        <v>6124900</v>
       </c>
       <c r="J17" s="3">
+        <v>5980400</v>
+      </c>
+      <c r="K17" s="3">
         <v>5515000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6362500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7332200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8417300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8281600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8374700</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>73200</v>
+        <v>67400</v>
       </c>
       <c r="E18" s="3">
-        <v>65200</v>
+        <v>69200</v>
       </c>
       <c r="F18" s="3">
-        <v>-13700</v>
+        <v>61700</v>
       </c>
       <c r="G18" s="3">
-        <v>128100</v>
+        <v>-13000</v>
       </c>
       <c r="H18" s="3">
-        <v>212800</v>
+        <v>121200</v>
       </c>
       <c r="I18" s="3">
-        <v>202000</v>
+        <v>201400</v>
       </c>
       <c r="J18" s="3">
+        <v>191200</v>
+      </c>
+      <c r="K18" s="3">
         <v>169100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>67800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>70300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>117800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>124100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-68700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>173800</v>
+        <v>119600</v>
       </c>
       <c r="E20" s="3">
-        <v>95300</v>
+        <v>149300</v>
       </c>
       <c r="F20" s="3">
-        <v>181600</v>
+        <v>90200</v>
       </c>
       <c r="G20" s="3">
-        <v>108300</v>
+        <v>171900</v>
       </c>
       <c r="H20" s="3">
-        <v>55700</v>
+        <v>102600</v>
       </c>
       <c r="I20" s="3">
-        <v>97600</v>
+        <v>52700</v>
       </c>
       <c r="J20" s="3">
+        <v>92400</v>
+      </c>
+      <c r="K20" s="3">
         <v>42800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>116600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>101700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>82400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>38600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>133500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>511600</v>
+        <v>435100</v>
       </c>
       <c r="E21" s="3">
-        <v>388700</v>
+        <v>467600</v>
       </c>
       <c r="F21" s="3">
-        <v>385600</v>
+        <v>366700</v>
       </c>
       <c r="G21" s="3">
-        <v>435600</v>
+        <v>363800</v>
       </c>
       <c r="H21" s="3">
-        <v>446300</v>
+        <v>411200</v>
       </c>
       <c r="I21" s="3">
-        <v>469500</v>
+        <v>421500</v>
       </c>
       <c r="J21" s="3">
+        <v>443500</v>
+      </c>
+      <c r="K21" s="3">
         <v>370200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>353600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>366200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>458800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>484700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>419800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>42700</v>
+        <v>58900</v>
       </c>
       <c r="E22" s="3">
-        <v>22700</v>
+        <v>40400</v>
       </c>
       <c r="F22" s="3">
-        <v>24200</v>
+        <v>21500</v>
       </c>
       <c r="G22" s="3">
-        <v>29200</v>
+        <v>22900</v>
       </c>
       <c r="H22" s="3">
-        <v>27500</v>
+        <v>27600</v>
       </c>
       <c r="I22" s="3">
-        <v>26800</v>
+        <v>26000</v>
       </c>
       <c r="J22" s="3">
+        <v>25400</v>
+      </c>
+      <c r="K22" s="3">
         <v>23500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>27300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>34100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>41700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>46100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47400</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>204200</v>
+        <v>128000</v>
       </c>
       <c r="E23" s="3">
-        <v>137700</v>
+        <v>178100</v>
       </c>
       <c r="F23" s="3">
-        <v>143700</v>
+        <v>130300</v>
       </c>
       <c r="G23" s="3">
-        <v>207300</v>
+        <v>136000</v>
       </c>
       <c r="H23" s="3">
-        <v>241000</v>
+        <v>196200</v>
       </c>
       <c r="I23" s="3">
-        <v>272700</v>
+        <v>228100</v>
       </c>
       <c r="J23" s="3">
+        <v>258200</v>
+      </c>
+      <c r="K23" s="3">
         <v>188500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>157100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>137900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>158500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>116600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>71800</v>
+        <v>73900</v>
       </c>
       <c r="E24" s="3">
-        <v>48500</v>
+        <v>65600</v>
       </c>
       <c r="F24" s="3">
-        <v>62100</v>
+        <v>45900</v>
       </c>
       <c r="G24" s="3">
-        <v>79200</v>
+        <v>58800</v>
       </c>
       <c r="H24" s="3">
-        <v>22300</v>
+        <v>75000</v>
       </c>
       <c r="I24" s="3">
-        <v>54900</v>
+        <v>21100</v>
       </c>
       <c r="J24" s="3">
+        <v>52000</v>
+      </c>
+      <c r="K24" s="3">
         <v>37300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>58400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>57100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>82800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>103900</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>132400</v>
+        <v>54100</v>
       </c>
       <c r="E26" s="3">
-        <v>89200</v>
+        <v>112500</v>
       </c>
       <c r="F26" s="3">
-        <v>81500</v>
+        <v>84500</v>
       </c>
       <c r="G26" s="3">
-        <v>128000</v>
+        <v>77200</v>
       </c>
       <c r="H26" s="3">
-        <v>218700</v>
+        <v>121200</v>
       </c>
       <c r="I26" s="3">
-        <v>217800</v>
+        <v>207000</v>
       </c>
       <c r="J26" s="3">
+        <v>206200</v>
+      </c>
+      <c r="K26" s="3">
         <v>151200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>98800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>80800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>75700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>52600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-86400</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>120700</v>
+        <v>41500</v>
       </c>
       <c r="E27" s="3">
-        <v>68000</v>
+        <v>101400</v>
       </c>
       <c r="F27" s="3">
-        <v>67400</v>
+        <v>64400</v>
       </c>
       <c r="G27" s="3">
-        <v>118900</v>
+        <v>63800</v>
       </c>
       <c r="H27" s="3">
-        <v>196200</v>
+        <v>112500</v>
       </c>
       <c r="I27" s="3">
-        <v>192400</v>
+        <v>185700</v>
       </c>
       <c r="J27" s="3">
+        <v>182100</v>
+      </c>
+      <c r="K27" s="3">
         <v>118400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>73600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>62700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>51400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>32500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-100600</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-173800</v>
+        <v>-119600</v>
       </c>
       <c r="E32" s="3">
-        <v>-95300</v>
+        <v>-149300</v>
       </c>
       <c r="F32" s="3">
-        <v>-181600</v>
+        <v>-90200</v>
       </c>
       <c r="G32" s="3">
-        <v>-108300</v>
+        <v>-171900</v>
       </c>
       <c r="H32" s="3">
-        <v>-55700</v>
+        <v>-102600</v>
       </c>
       <c r="I32" s="3">
-        <v>-97600</v>
+        <v>-52700</v>
       </c>
       <c r="J32" s="3">
+        <v>-92400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-42800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-116600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-101700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-82400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-38600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-133500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>120700</v>
+        <v>41500</v>
       </c>
       <c r="E33" s="3">
-        <v>68000</v>
+        <v>101400</v>
       </c>
       <c r="F33" s="3">
-        <v>67400</v>
+        <v>64400</v>
       </c>
       <c r="G33" s="3">
-        <v>118900</v>
+        <v>63800</v>
       </c>
       <c r="H33" s="3">
-        <v>196200</v>
+        <v>112500</v>
       </c>
       <c r="I33" s="3">
-        <v>192400</v>
+        <v>185700</v>
       </c>
       <c r="J33" s="3">
+        <v>182100</v>
+      </c>
+      <c r="K33" s="3">
         <v>118400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>73600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>62700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>51400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>32500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-100600</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>120700</v>
+        <v>41500</v>
       </c>
       <c r="E35" s="3">
-        <v>68000</v>
+        <v>101400</v>
       </c>
       <c r="F35" s="3">
-        <v>67400</v>
+        <v>64400</v>
       </c>
       <c r="G35" s="3">
-        <v>118900</v>
+        <v>63800</v>
       </c>
       <c r="H35" s="3">
-        <v>196200</v>
+        <v>112500</v>
       </c>
       <c r="I35" s="3">
-        <v>192400</v>
+        <v>185700</v>
       </c>
       <c r="J35" s="3">
+        <v>182100</v>
+      </c>
+      <c r="K35" s="3">
         <v>118400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>73600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>62700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>51400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>32500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-100600</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,79 +1986,83 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>319700</v>
+        <v>312000</v>
       </c>
       <c r="E41" s="3">
-        <v>439100</v>
+        <v>302600</v>
       </c>
       <c r="F41" s="3">
-        <v>568600</v>
+        <v>415700</v>
       </c>
       <c r="G41" s="3">
-        <v>366400</v>
+        <v>538200</v>
       </c>
       <c r="H41" s="3">
-        <v>300800</v>
+        <v>346800</v>
       </c>
       <c r="I41" s="3">
-        <v>341300</v>
+        <v>284700</v>
       </c>
       <c r="J41" s="3">
+        <v>323100</v>
+      </c>
+      <c r="K41" s="3">
         <v>317900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>385900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>256000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>244700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>284500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>300500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>34600</v>
+        <v>30300</v>
       </c>
       <c r="E42" s="3">
-        <v>22000</v>
+        <v>32700</v>
       </c>
       <c r="F42" s="3">
-        <v>19700</v>
+        <v>20800</v>
       </c>
       <c r="G42" s="3">
-        <v>6100</v>
+        <v>18600</v>
       </c>
       <c r="H42" s="3">
-        <v>16000</v>
+        <v>5700</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100</v>
-      </c>
-      <c r="L42" s="3">
-        <v>200</v>
       </c>
       <c r="M42" s="3">
         <v>200</v>
@@ -1982,305 +2071,329 @@
         <v>200</v>
       </c>
       <c r="O42" s="3">
+        <v>200</v>
+      </c>
+      <c r="P42" s="3">
         <v>1000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1537800</v>
+        <v>1559900</v>
       </c>
       <c r="E43" s="3">
-        <v>1545300</v>
+        <v>1455700</v>
       </c>
       <c r="F43" s="3">
-        <v>1287600</v>
+        <v>1462800</v>
       </c>
       <c r="G43" s="3">
-        <v>1289100</v>
+        <v>1218800</v>
       </c>
       <c r="H43" s="3">
-        <v>1471100</v>
+        <v>1220200</v>
       </c>
       <c r="I43" s="3">
-        <v>1503800</v>
+        <v>1392500</v>
       </c>
       <c r="J43" s="3">
+        <v>1423500</v>
+      </c>
+      <c r="K43" s="3">
         <v>1332000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1364300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1612800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1812600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2010800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1998800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1161300</v>
+        <v>1171700</v>
       </c>
       <c r="E44" s="3">
-        <v>1106100</v>
+        <v>1099200</v>
       </c>
       <c r="F44" s="3">
-        <v>814400</v>
+        <v>1047100</v>
       </c>
       <c r="G44" s="3">
-        <v>780900</v>
+        <v>770900</v>
       </c>
       <c r="H44" s="3">
-        <v>828300</v>
+        <v>739200</v>
       </c>
       <c r="I44" s="3">
-        <v>766900</v>
+        <v>784000</v>
       </c>
       <c r="J44" s="3">
+        <v>726000</v>
+      </c>
+      <c r="K44" s="3">
         <v>703300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>684800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>848200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>858000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>947600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>857800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>227800</v>
+        <v>229500</v>
       </c>
       <c r="E45" s="3">
-        <v>277400</v>
+        <v>215700</v>
       </c>
       <c r="F45" s="3">
-        <v>206600</v>
+        <v>262600</v>
       </c>
       <c r="G45" s="3">
-        <v>160400</v>
+        <v>195600</v>
       </c>
       <c r="H45" s="3">
-        <v>218200</v>
+        <v>151900</v>
       </c>
       <c r="I45" s="3">
-        <v>260000</v>
+        <v>206500</v>
       </c>
       <c r="J45" s="3">
+        <v>246100</v>
+      </c>
+      <c r="K45" s="3">
         <v>223700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>240600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>428800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>382100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>326100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>368300</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3281200</v>
+        <v>3303400</v>
       </c>
       <c r="E46" s="3">
-        <v>3390000</v>
+        <v>3105900</v>
       </c>
       <c r="F46" s="3">
-        <v>2896900</v>
+        <v>3208900</v>
       </c>
       <c r="G46" s="3">
-        <v>2602800</v>
+        <v>2742200</v>
       </c>
       <c r="H46" s="3">
-        <v>2834300</v>
+        <v>2463800</v>
       </c>
       <c r="I46" s="3">
-        <v>2805100</v>
+        <v>2682900</v>
       </c>
       <c r="J46" s="3">
+        <v>2655300</v>
+      </c>
+      <c r="K46" s="3">
         <v>2577400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2675600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3146000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3297700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3569100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3526400</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1643300</v>
+        <v>842400</v>
       </c>
       <c r="E47" s="3">
-        <v>821900</v>
+        <v>1555600</v>
       </c>
       <c r="F47" s="3">
-        <v>739000</v>
+        <v>778000</v>
       </c>
       <c r="G47" s="3">
-        <v>716700</v>
+        <v>699500</v>
       </c>
       <c r="H47" s="3">
-        <v>837200</v>
+        <v>678400</v>
       </c>
       <c r="I47" s="3">
-        <v>924200</v>
+        <v>792500</v>
       </c>
       <c r="J47" s="3">
+        <v>874900</v>
+      </c>
+      <c r="K47" s="3">
         <v>883300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>832500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1175900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1246200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1047700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>934400</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2134100</v>
+        <v>1777700</v>
       </c>
       <c r="E48" s="3">
-        <v>1753500</v>
+        <v>2020100</v>
       </c>
       <c r="F48" s="3">
-        <v>1663100</v>
+        <v>1659800</v>
       </c>
       <c r="G48" s="3">
-        <v>1713400</v>
+        <v>1574200</v>
       </c>
       <c r="H48" s="3">
-        <v>1545900</v>
+        <v>1621900</v>
       </c>
       <c r="I48" s="3">
-        <v>1624500</v>
+        <v>1463300</v>
       </c>
       <c r="J48" s="3">
+        <v>1537700</v>
+      </c>
+      <c r="K48" s="3">
         <v>1385000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1444600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1699300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1750200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2546000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2369600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>136400</v>
+        <v>129400</v>
       </c>
       <c r="E49" s="3">
-        <v>138300</v>
+        <v>129100</v>
       </c>
       <c r="F49" s="3">
-        <v>136500</v>
+        <v>130900</v>
       </c>
       <c r="G49" s="3">
-        <v>108500</v>
+        <v>129200</v>
       </c>
       <c r="H49" s="3">
-        <v>82300</v>
+        <v>102700</v>
       </c>
       <c r="I49" s="3">
-        <v>76200</v>
+        <v>77900</v>
       </c>
       <c r="J49" s="3">
+        <v>72100</v>
+      </c>
+      <c r="K49" s="3">
         <v>65700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>62600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>77000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>87900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>114700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>126300</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>259400</v>
+        <v>231400</v>
       </c>
       <c r="E52" s="3">
-        <v>204200</v>
+        <v>245500</v>
       </c>
       <c r="F52" s="3">
-        <v>172500</v>
+        <v>193300</v>
       </c>
       <c r="G52" s="3">
-        <v>214300</v>
+        <v>163300</v>
       </c>
       <c r="H52" s="3">
-        <v>213900</v>
+        <v>202800</v>
       </c>
       <c r="I52" s="3">
-        <v>224800</v>
+        <v>202400</v>
       </c>
       <c r="J52" s="3">
+        <v>212800</v>
+      </c>
+      <c r="K52" s="3">
         <v>144500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>171700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>163800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>166000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>173600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>185800</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6291600</v>
+        <v>6284300</v>
       </c>
       <c r="E54" s="3">
-        <v>6307800</v>
+        <v>5955500</v>
       </c>
       <c r="F54" s="3">
-        <v>5608000</v>
+        <v>5970900</v>
       </c>
       <c r="G54" s="3">
-        <v>5355700</v>
+        <v>5308400</v>
       </c>
       <c r="H54" s="3">
-        <v>5513500</v>
+        <v>5069700</v>
       </c>
       <c r="I54" s="3">
-        <v>5450200</v>
+        <v>5219000</v>
       </c>
       <c r="J54" s="3">
+        <v>5159100</v>
+      </c>
+      <c r="K54" s="3">
         <v>5055800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5187100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6262100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6548000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7451100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7142600</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>845300</v>
+        <v>821600</v>
       </c>
       <c r="E57" s="3">
-        <v>862600</v>
+        <v>800100</v>
       </c>
       <c r="F57" s="3">
-        <v>778500</v>
+        <v>816600</v>
       </c>
       <c r="G57" s="3">
-        <v>752100</v>
+        <v>736900</v>
       </c>
       <c r="H57" s="3">
-        <v>885800</v>
+        <v>711900</v>
       </c>
       <c r="I57" s="3">
-        <v>838400</v>
+        <v>838500</v>
       </c>
       <c r="J57" s="3">
+        <v>793600</v>
+      </c>
+      <c r="K57" s="3">
         <v>728500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>737900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>941700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>956100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1210100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1102900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2111000</v>
+        <v>1102900</v>
       </c>
       <c r="E58" s="3">
-        <v>1149500</v>
+        <v>1998200</v>
       </c>
       <c r="F58" s="3">
-        <v>910100</v>
+        <v>1088100</v>
       </c>
       <c r="G58" s="3">
-        <v>856500</v>
+        <v>861500</v>
       </c>
       <c r="H58" s="3">
-        <v>719200</v>
+        <v>810700</v>
       </c>
       <c r="I58" s="3">
-        <v>783700</v>
+        <v>680800</v>
       </c>
       <c r="J58" s="3">
+        <v>741900</v>
+      </c>
+      <c r="K58" s="3">
         <v>676100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>910000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>910600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1099300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1157900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1432100</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1099000</v>
+        <v>633200</v>
       </c>
       <c r="E59" s="3">
-        <v>547100</v>
+        <v>1040300</v>
       </c>
       <c r="F59" s="3">
-        <v>435800</v>
+        <v>517900</v>
       </c>
       <c r="G59" s="3">
-        <v>545800</v>
+        <v>412600</v>
       </c>
       <c r="H59" s="3">
-        <v>630100</v>
+        <v>516700</v>
       </c>
       <c r="I59" s="3">
-        <v>604400</v>
+        <v>596500</v>
       </c>
       <c r="J59" s="3">
+        <v>572100</v>
+      </c>
+      <c r="K59" s="3">
         <v>572700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>552200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>597100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>636400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>612300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>590100</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2568100</v>
+        <v>2557700</v>
       </c>
       <c r="E60" s="3">
-        <v>2559300</v>
+        <v>2430900</v>
       </c>
       <c r="F60" s="3">
-        <v>2124500</v>
+        <v>2422600</v>
       </c>
       <c r="G60" s="3">
-        <v>2154400</v>
+        <v>2011000</v>
       </c>
       <c r="H60" s="3">
-        <v>2235100</v>
+        <v>2039300</v>
       </c>
       <c r="I60" s="3">
-        <v>2226500</v>
+        <v>2115700</v>
       </c>
       <c r="J60" s="3">
+        <v>2107500</v>
+      </c>
+      <c r="K60" s="3">
         <v>1977300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2200200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2449400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2691800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2980300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3125100</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1041600</v>
+        <v>1101700</v>
       </c>
       <c r="E61" s="3">
-        <v>1218000</v>
+        <v>986000</v>
       </c>
       <c r="F61" s="3">
-        <v>1099900</v>
+        <v>1152900</v>
       </c>
       <c r="G61" s="3">
-        <v>889900</v>
+        <v>1041100</v>
       </c>
       <c r="H61" s="3">
-        <v>938900</v>
+        <v>842400</v>
       </c>
       <c r="I61" s="3">
-        <v>958600</v>
+        <v>888700</v>
       </c>
       <c r="J61" s="3">
+        <v>907400</v>
+      </c>
+      <c r="K61" s="3">
         <v>1026100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1005500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1431200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1445800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1755400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1507900</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>508300</v>
+        <v>340600</v>
       </c>
       <c r="E62" s="3">
-        <v>413700</v>
+        <v>481200</v>
       </c>
       <c r="F62" s="3">
-        <v>418100</v>
+        <v>391600</v>
       </c>
       <c r="G62" s="3">
-        <v>471200</v>
+        <v>395800</v>
       </c>
       <c r="H62" s="3">
-        <v>452900</v>
+        <v>446000</v>
       </c>
       <c r="I62" s="3">
-        <v>495500</v>
+        <v>428700</v>
       </c>
       <c r="J62" s="3">
+        <v>469000</v>
+      </c>
+      <c r="K62" s="3">
         <v>454800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>521800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>549800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>580800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>689700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>723500</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4258400</v>
+        <v>4190900</v>
       </c>
       <c r="E66" s="3">
-        <v>4425900</v>
+        <v>4031000</v>
       </c>
       <c r="F66" s="3">
-        <v>3856500</v>
+        <v>4189500</v>
       </c>
       <c r="G66" s="3">
-        <v>3736200</v>
+        <v>3650500</v>
       </c>
       <c r="H66" s="3">
-        <v>3844200</v>
+        <v>3536700</v>
       </c>
       <c r="I66" s="3">
-        <v>3856000</v>
+        <v>3638900</v>
       </c>
       <c r="J66" s="3">
+        <v>3650100</v>
+      </c>
+      <c r="K66" s="3">
         <v>3662600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3914300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4635100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4924500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5944500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5834500</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1292500</v>
+        <v>1230400</v>
       </c>
       <c r="E72" s="3">
-        <v>1175100</v>
+        <v>1223400</v>
       </c>
       <c r="F72" s="3">
-        <v>1136000</v>
+        <v>1112300</v>
       </c>
       <c r="G72" s="3">
-        <v>1112800</v>
+        <v>1075300</v>
       </c>
       <c r="H72" s="3">
-        <v>1022800</v>
+        <v>1053300</v>
       </c>
       <c r="I72" s="3">
-        <v>863600</v>
+        <v>968100</v>
       </c>
       <c r="J72" s="3">
+        <v>817500</v>
+      </c>
+      <c r="K72" s="3">
         <v>700600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>663800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>710300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>725600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>692000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>655200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2033100</v>
+        <v>2093400</v>
       </c>
       <c r="E76" s="3">
-        <v>1881900</v>
+        <v>1924500</v>
       </c>
       <c r="F76" s="3">
-        <v>1751500</v>
+        <v>1781400</v>
       </c>
       <c r="G76" s="3">
-        <v>1619500</v>
+        <v>1658000</v>
       </c>
       <c r="H76" s="3">
-        <v>1669200</v>
+        <v>1533000</v>
       </c>
       <c r="I76" s="3">
-        <v>1594100</v>
+        <v>1580100</v>
       </c>
       <c r="J76" s="3">
+        <v>1509000</v>
+      </c>
+      <c r="K76" s="3">
         <v>1393200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1272700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1627000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1623500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1506600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1308000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>120700</v>
+        <v>41500</v>
       </c>
       <c r="E81" s="3">
-        <v>68000</v>
+        <v>101400</v>
       </c>
       <c r="F81" s="3">
-        <v>67400</v>
+        <v>64400</v>
       </c>
       <c r="G81" s="3">
-        <v>118900</v>
+        <v>63800</v>
       </c>
       <c r="H81" s="3">
-        <v>196200</v>
+        <v>112500</v>
       </c>
       <c r="I81" s="3">
-        <v>192400</v>
+        <v>185700</v>
       </c>
       <c r="J81" s="3">
+        <v>182100</v>
+      </c>
+      <c r="K81" s="3">
         <v>118400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>73600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>62700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>51400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>32500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-100600</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>263500</v>
+        <v>248500</v>
       </c>
       <c r="E83" s="3">
-        <v>227300</v>
+        <v>249400</v>
       </c>
       <c r="F83" s="3">
-        <v>216800</v>
+        <v>215100</v>
       </c>
       <c r="G83" s="3">
-        <v>198300</v>
+        <v>205200</v>
       </c>
       <c r="H83" s="3">
-        <v>177100</v>
+        <v>187700</v>
       </c>
       <c r="I83" s="3">
-        <v>169200</v>
+        <v>167600</v>
       </c>
       <c r="J83" s="3">
+        <v>160200</v>
+      </c>
+      <c r="K83" s="3">
         <v>157500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>170800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>192000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>257500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>321300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>354500</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>254200</v>
+        <v>205700</v>
       </c>
       <c r="E89" s="3">
-        <v>-85500</v>
+        <v>240600</v>
       </c>
       <c r="F89" s="3">
-        <v>-3400</v>
+        <v>-80900</v>
       </c>
       <c r="G89" s="3">
-        <v>286000</v>
+        <v>-3200</v>
       </c>
       <c r="H89" s="3">
-        <v>314600</v>
+        <v>270700</v>
       </c>
       <c r="I89" s="3">
-        <v>261700</v>
+        <v>297800</v>
       </c>
       <c r="J89" s="3">
+        <v>247800</v>
+      </c>
+      <c r="K89" s="3">
         <v>280000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>313000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>356300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>500500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>278200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-241800</v>
+        <v>-232400</v>
       </c>
       <c r="E91" s="3">
-        <v>-246000</v>
+        <v>-228900</v>
       </c>
       <c r="F91" s="3">
-        <v>-225000</v>
+        <v>-232800</v>
       </c>
       <c r="G91" s="3">
-        <v>-318900</v>
+        <v>-213000</v>
       </c>
       <c r="H91" s="3">
-        <v>-290200</v>
+        <v>-301900</v>
       </c>
       <c r="I91" s="3">
-        <v>-231500</v>
+        <v>-274700</v>
       </c>
       <c r="J91" s="3">
+        <v>-219100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-191700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-188500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-236100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-360600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-415900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-277000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-146100</v>
+        <v>-158200</v>
       </c>
       <c r="E94" s="3">
-        <v>-270100</v>
+        <v>-138300</v>
       </c>
       <c r="F94" s="3">
-        <v>-12900</v>
+        <v>-255700</v>
       </c>
       <c r="G94" s="3">
-        <v>-223200</v>
+        <v>-12200</v>
       </c>
       <c r="H94" s="3">
-        <v>-209200</v>
+        <v>-211300</v>
       </c>
       <c r="I94" s="3">
-        <v>-231300</v>
+        <v>-198000</v>
       </c>
       <c r="J94" s="3">
+        <v>-219000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-245100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-369100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-408500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-183100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-28500</v>
+        <v>-36000</v>
       </c>
       <c r="E96" s="3">
-        <v>-28600</v>
+        <v>-27000</v>
       </c>
       <c r="F96" s="3">
-        <v>-40400</v>
+        <v>-27100</v>
       </c>
       <c r="G96" s="3">
-        <v>-40400</v>
+        <v>-38300</v>
       </c>
       <c r="H96" s="3">
-        <v>-38100</v>
+        <v>-38300</v>
       </c>
       <c r="I96" s="3">
-        <v>-26200</v>
+        <v>-36000</v>
       </c>
       <c r="J96" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-19000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-15500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-18000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-19400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-35100</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-232400</v>
+        <v>-59500</v>
       </c>
       <c r="E100" s="3">
-        <v>236000</v>
+        <v>-220000</v>
       </c>
       <c r="F100" s="3">
-        <v>236800</v>
+        <v>223400</v>
       </c>
       <c r="G100" s="3">
-        <v>-1200</v>
+        <v>224200</v>
       </c>
       <c r="H100" s="3">
-        <v>-130900</v>
+        <v>-1100</v>
       </c>
       <c r="I100" s="3">
-        <v>-13100</v>
+        <v>-123900</v>
       </c>
       <c r="J100" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-69900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-153900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-132500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>274000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-103600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-206500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>18500</v>
+        <v>19300</v>
       </c>
       <c r="E101" s="3">
-        <v>-12200</v>
+        <v>17500</v>
       </c>
       <c r="F101" s="3">
-        <v>-4000</v>
+        <v>-11600</v>
       </c>
       <c r="G101" s="3">
-        <v>-6300</v>
+        <v>-3800</v>
       </c>
       <c r="H101" s="3">
-        <v>5700</v>
+        <v>-5900</v>
       </c>
       <c r="I101" s="3">
-        <v>7000</v>
+        <v>5400</v>
       </c>
       <c r="J101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K101" s="3">
         <v>-2100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>12500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>15200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-7100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-105700</v>
+        <v>7300</v>
       </c>
       <c r="E102" s="3">
-        <v>-131800</v>
+        <v>-100100</v>
       </c>
       <c r="F102" s="3">
-        <v>216600</v>
+        <v>-124800</v>
       </c>
       <c r="G102" s="3">
-        <v>55400</v>
+        <v>205000</v>
       </c>
       <c r="H102" s="3">
-        <v>-19700</v>
+        <v>52400</v>
       </c>
       <c r="I102" s="3">
-        <v>24300</v>
+        <v>-18600</v>
       </c>
       <c r="J102" s="3">
+        <v>23000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-37100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>163000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>35600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-47200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-118500</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6740600</v>
+        <v>7501300</v>
       </c>
       <c r="E8" s="3">
-        <v>6803200</v>
+        <v>7570900</v>
       </c>
       <c r="F8" s="3">
-        <v>5936600</v>
+        <v>6606500</v>
       </c>
       <c r="G8" s="3">
-        <v>5178000</v>
+        <v>5762400</v>
       </c>
       <c r="H8" s="3">
-        <v>5834100</v>
+        <v>6492500</v>
       </c>
       <c r="I8" s="3">
-        <v>6326300</v>
+        <v>7040300</v>
       </c>
       <c r="J8" s="3">
-        <v>6171600</v>
+        <v>6868100</v>
       </c>
       <c r="K8" s="3">
         <v>5684100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5726300</v>
+        <v>6372500</v>
       </c>
       <c r="E9" s="3">
-        <v>11606800</v>
+        <v>6458300</v>
       </c>
       <c r="F9" s="3">
-        <v>5051700</v>
+        <v>5621800</v>
       </c>
       <c r="G9" s="3">
-        <v>4353000</v>
+        <v>4844200</v>
       </c>
       <c r="H9" s="3">
-        <v>4875600</v>
+        <v>5425800</v>
       </c>
       <c r="I9" s="3">
-        <v>5260200</v>
+        <v>5853800</v>
       </c>
       <c r="J9" s="3">
-        <v>5113000</v>
+        <v>5690000</v>
       </c>
       <c r="K9" s="3">
         <v>4644900</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1014400</v>
+        <v>1128900</v>
       </c>
       <c r="E10" s="3">
-        <v>-4803600</v>
+        <v>1112600</v>
       </c>
       <c r="F10" s="3">
-        <v>884900</v>
+        <v>984700</v>
       </c>
       <c r="G10" s="3">
-        <v>825000</v>
+        <v>918100</v>
       </c>
       <c r="H10" s="3">
-        <v>958500</v>
+        <v>1066700</v>
       </c>
       <c r="I10" s="3">
-        <v>1066200</v>
+        <v>1186500</v>
       </c>
       <c r="J10" s="3">
-        <v>1058600</v>
+        <v>1178000</v>
       </c>
       <c r="K10" s="3">
         <v>1039200</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>148800</v>
       </c>
       <c r="E12" s="3">
-        <v>123200</v>
+        <v>137100</v>
       </c>
       <c r="F12" s="3">
-        <v>109800</v>
+        <v>122200</v>
       </c>
       <c r="G12" s="3">
-        <v>104200</v>
+        <v>116000</v>
       </c>
       <c r="H12" s="3">
-        <v>109600</v>
+        <v>122000</v>
       </c>
       <c r="I12" s="3">
+        <v>122500</v>
+      </c>
+      <c r="J12" s="3">
         <v>110100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>98900</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E14" s="3">
-        <v>55000</v>
+        <v>61200</v>
       </c>
       <c r="F14" s="3">
-        <v>11200</v>
+        <v>12500</v>
       </c>
       <c r="G14" s="3">
-        <v>66800</v>
+        <v>74300</v>
       </c>
       <c r="H14" s="3">
-        <v>29100</v>
+        <v>32400</v>
       </c>
       <c r="I14" s="3">
-        <v>59200</v>
+        <v>65800</v>
       </c>
       <c r="J14" s="3">
-        <v>94700</v>
+        <v>105300</v>
       </c>
       <c r="K14" s="3">
         <v>91200</v>
@@ -1014,26 +1014,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>38500</v>
       </c>
       <c r="E15" s="3">
-        <v>33000</v>
+        <v>36700</v>
       </c>
       <c r="F15" s="3">
-        <v>24100</v>
+        <v>26800</v>
       </c>
       <c r="G15" s="3">
-        <v>27400</v>
+        <v>30500</v>
       </c>
       <c r="H15" s="3">
-        <v>21400</v>
+        <v>23900</v>
       </c>
       <c r="I15" s="3">
-        <v>17000</v>
+        <v>18900</v>
       </c>
       <c r="J15" s="3">
-        <v>16500</v>
+        <v>18400</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6673300</v>
+        <v>7426400</v>
       </c>
       <c r="E17" s="3">
-        <v>6733900</v>
+        <v>7493900</v>
       </c>
       <c r="F17" s="3">
-        <v>5874900</v>
+        <v>6537900</v>
       </c>
       <c r="G17" s="3">
-        <v>5191000</v>
+        <v>5776800</v>
       </c>
       <c r="H17" s="3">
-        <v>5712900</v>
+        <v>6357600</v>
       </c>
       <c r="I17" s="3">
-        <v>6124900</v>
+        <v>6816100</v>
       </c>
       <c r="J17" s="3">
-        <v>5980400</v>
+        <v>6655300</v>
       </c>
       <c r="K17" s="3">
         <v>5515000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>67400</v>
+        <v>75000</v>
       </c>
       <c r="E18" s="3">
-        <v>69200</v>
+        <v>77100</v>
       </c>
       <c r="F18" s="3">
-        <v>61700</v>
+        <v>68600</v>
       </c>
       <c r="G18" s="3">
-        <v>-13000</v>
+        <v>-14500</v>
       </c>
       <c r="H18" s="3">
-        <v>121200</v>
+        <v>134900</v>
       </c>
       <c r="I18" s="3">
-        <v>201400</v>
+        <v>224100</v>
       </c>
       <c r="J18" s="3">
-        <v>191200</v>
+        <v>212800</v>
       </c>
       <c r="K18" s="3">
         <v>169100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>119600</v>
+        <v>133100</v>
       </c>
       <c r="E20" s="3">
-        <v>149300</v>
+        <v>166100</v>
       </c>
       <c r="F20" s="3">
-        <v>90200</v>
+        <v>100400</v>
       </c>
       <c r="G20" s="3">
-        <v>171900</v>
+        <v>191300</v>
       </c>
       <c r="H20" s="3">
-        <v>102600</v>
+        <v>114100</v>
       </c>
       <c r="I20" s="3">
-        <v>52700</v>
+        <v>58700</v>
       </c>
       <c r="J20" s="3">
-        <v>92400</v>
+        <v>102800</v>
       </c>
       <c r="K20" s="3">
         <v>42800</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>435100</v>
+        <v>482600</v>
       </c>
       <c r="E21" s="3">
-        <v>467600</v>
+        <v>518900</v>
       </c>
       <c r="F21" s="3">
-        <v>366700</v>
+        <v>406700</v>
       </c>
       <c r="G21" s="3">
-        <v>363800</v>
+        <v>403600</v>
       </c>
       <c r="H21" s="3">
-        <v>411200</v>
+        <v>456500</v>
       </c>
       <c r="I21" s="3">
-        <v>421500</v>
+        <v>468000</v>
       </c>
       <c r="J21" s="3">
-        <v>443500</v>
+        <v>492500</v>
       </c>
       <c r="K21" s="3">
         <v>370200</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>58900</v>
+        <v>65600</v>
       </c>
       <c r="E22" s="3">
-        <v>40400</v>
+        <v>45000</v>
       </c>
       <c r="F22" s="3">
-        <v>21500</v>
+        <v>24000</v>
       </c>
       <c r="G22" s="3">
-        <v>22900</v>
+        <v>25500</v>
       </c>
       <c r="H22" s="3">
-        <v>27600</v>
+        <v>30700</v>
       </c>
       <c r="I22" s="3">
-        <v>26000</v>
+        <v>28900</v>
       </c>
       <c r="J22" s="3">
-        <v>25400</v>
+        <v>28200</v>
       </c>
       <c r="K22" s="3">
         <v>23500</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>128000</v>
+        <v>142500</v>
       </c>
       <c r="E23" s="3">
-        <v>178100</v>
+        <v>198200</v>
       </c>
       <c r="F23" s="3">
-        <v>130300</v>
+        <v>145100</v>
       </c>
       <c r="G23" s="3">
-        <v>136000</v>
+        <v>151300</v>
       </c>
       <c r="H23" s="3">
-        <v>196200</v>
+        <v>218300</v>
       </c>
       <c r="I23" s="3">
-        <v>228100</v>
+        <v>253900</v>
       </c>
       <c r="J23" s="3">
-        <v>258200</v>
+        <v>287300</v>
       </c>
       <c r="K23" s="3">
         <v>188500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>73900</v>
+        <v>82300</v>
       </c>
       <c r="E24" s="3">
-        <v>65600</v>
+        <v>73100</v>
       </c>
       <c r="F24" s="3">
-        <v>45900</v>
+        <v>51000</v>
       </c>
       <c r="G24" s="3">
-        <v>58800</v>
+        <v>65500</v>
       </c>
       <c r="H24" s="3">
-        <v>75000</v>
+        <v>83500</v>
       </c>
       <c r="I24" s="3">
-        <v>21100</v>
+        <v>23500</v>
       </c>
       <c r="J24" s="3">
-        <v>52000</v>
+        <v>57900</v>
       </c>
       <c r="K24" s="3">
         <v>37300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>54100</v>
+        <v>60200</v>
       </c>
       <c r="E26" s="3">
-        <v>112500</v>
+        <v>125200</v>
       </c>
       <c r="F26" s="3">
-        <v>84500</v>
+        <v>94000</v>
       </c>
       <c r="G26" s="3">
-        <v>77200</v>
+        <v>85900</v>
       </c>
       <c r="H26" s="3">
-        <v>121200</v>
+        <v>134900</v>
       </c>
       <c r="I26" s="3">
-        <v>207000</v>
+        <v>230400</v>
       </c>
       <c r="J26" s="3">
-        <v>206200</v>
+        <v>229400</v>
       </c>
       <c r="K26" s="3">
         <v>151200</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>41500</v>
+        <v>46200</v>
       </c>
       <c r="E27" s="3">
-        <v>101400</v>
+        <v>112800</v>
       </c>
       <c r="F27" s="3">
-        <v>64400</v>
+        <v>71700</v>
       </c>
       <c r="G27" s="3">
-        <v>63800</v>
+        <v>71000</v>
       </c>
       <c r="H27" s="3">
-        <v>112500</v>
+        <v>125200</v>
       </c>
       <c r="I27" s="3">
-        <v>185700</v>
+        <v>206700</v>
       </c>
       <c r="J27" s="3">
-        <v>182100</v>
+        <v>202700</v>
       </c>
       <c r="K27" s="3">
         <v>118400</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-119600</v>
+        <v>-133100</v>
       </c>
       <c r="E32" s="3">
-        <v>-149300</v>
+        <v>-166100</v>
       </c>
       <c r="F32" s="3">
-        <v>-90200</v>
+        <v>-100400</v>
       </c>
       <c r="G32" s="3">
-        <v>-171900</v>
+        <v>-191300</v>
       </c>
       <c r="H32" s="3">
-        <v>-102600</v>
+        <v>-114100</v>
       </c>
       <c r="I32" s="3">
-        <v>-52700</v>
+        <v>-58700</v>
       </c>
       <c r="J32" s="3">
-        <v>-92400</v>
+        <v>-102800</v>
       </c>
       <c r="K32" s="3">
         <v>-42800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>41500</v>
+        <v>46200</v>
       </c>
       <c r="E33" s="3">
-        <v>101400</v>
+        <v>112800</v>
       </c>
       <c r="F33" s="3">
-        <v>64400</v>
+        <v>71700</v>
       </c>
       <c r="G33" s="3">
-        <v>63800</v>
+        <v>71000</v>
       </c>
       <c r="H33" s="3">
-        <v>112500</v>
+        <v>125200</v>
       </c>
       <c r="I33" s="3">
-        <v>185700</v>
+        <v>206700</v>
       </c>
       <c r="J33" s="3">
-        <v>182100</v>
+        <v>202700</v>
       </c>
       <c r="K33" s="3">
         <v>118400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>41500</v>
+        <v>46200</v>
       </c>
       <c r="E35" s="3">
-        <v>101400</v>
+        <v>112800</v>
       </c>
       <c r="F35" s="3">
-        <v>64400</v>
+        <v>71700</v>
       </c>
       <c r="G35" s="3">
-        <v>63800</v>
+        <v>71000</v>
       </c>
       <c r="H35" s="3">
-        <v>112500</v>
+        <v>125200</v>
       </c>
       <c r="I35" s="3">
-        <v>185700</v>
+        <v>206700</v>
       </c>
       <c r="J35" s="3">
-        <v>182100</v>
+        <v>202700</v>
       </c>
       <c r="K35" s="3">
         <v>118400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>312000</v>
+        <v>347200</v>
       </c>
       <c r="E41" s="3">
-        <v>302600</v>
+        <v>336800</v>
       </c>
       <c r="F41" s="3">
-        <v>415700</v>
+        <v>462600</v>
       </c>
       <c r="G41" s="3">
-        <v>538200</v>
+        <v>599000</v>
       </c>
       <c r="H41" s="3">
-        <v>346800</v>
+        <v>385900</v>
       </c>
       <c r="I41" s="3">
-        <v>284700</v>
+        <v>316900</v>
       </c>
       <c r="J41" s="3">
-        <v>323100</v>
+        <v>359500</v>
       </c>
       <c r="K41" s="3">
         <v>317900</v>
@@ -2038,22 +2038,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>30300</v>
+        <v>33700</v>
       </c>
       <c r="E42" s="3">
-        <v>32700</v>
+        <v>36400</v>
       </c>
       <c r="F42" s="3">
+        <v>23100</v>
+      </c>
+      <c r="G42" s="3">
         <v>20800</v>
       </c>
-      <c r="G42" s="3">
-        <v>18600</v>
-      </c>
       <c r="H42" s="3">
-        <v>5700</v>
+        <v>6400</v>
       </c>
       <c r="I42" s="3">
-        <v>15100</v>
+        <v>16800</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1559900</v>
+        <v>1736000</v>
       </c>
       <c r="E43" s="3">
-        <v>1455700</v>
+        <v>1619900</v>
       </c>
       <c r="F43" s="3">
-        <v>1462800</v>
+        <v>1627900</v>
       </c>
       <c r="G43" s="3">
-        <v>1218800</v>
+        <v>1356400</v>
       </c>
       <c r="H43" s="3">
-        <v>1220200</v>
+        <v>1357900</v>
       </c>
       <c r="I43" s="3">
-        <v>1392500</v>
+        <v>1549600</v>
       </c>
       <c r="J43" s="3">
-        <v>1423500</v>
+        <v>1584200</v>
       </c>
       <c r="K43" s="3">
         <v>1332000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1171700</v>
+        <v>1303900</v>
       </c>
       <c r="E44" s="3">
-        <v>1099200</v>
+        <v>1223300</v>
       </c>
       <c r="F44" s="3">
-        <v>1047100</v>
+        <v>1165200</v>
       </c>
       <c r="G44" s="3">
-        <v>770900</v>
+        <v>857900</v>
       </c>
       <c r="H44" s="3">
-        <v>739200</v>
+        <v>822600</v>
       </c>
       <c r="I44" s="3">
-        <v>784000</v>
+        <v>872500</v>
       </c>
       <c r="J44" s="3">
-        <v>726000</v>
+        <v>807900</v>
       </c>
       <c r="K44" s="3">
         <v>703300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>229500</v>
+        <v>255400</v>
       </c>
       <c r="E45" s="3">
-        <v>215700</v>
+        <v>240000</v>
       </c>
       <c r="F45" s="3">
-        <v>262600</v>
+        <v>292200</v>
       </c>
       <c r="G45" s="3">
-        <v>195600</v>
+        <v>217700</v>
       </c>
       <c r="H45" s="3">
-        <v>151900</v>
+        <v>169000</v>
       </c>
       <c r="I45" s="3">
-        <v>206500</v>
+        <v>229800</v>
       </c>
       <c r="J45" s="3">
-        <v>246100</v>
+        <v>273900</v>
       </c>
       <c r="K45" s="3">
         <v>223700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3303400</v>
+        <v>3676100</v>
       </c>
       <c r="E46" s="3">
-        <v>3105900</v>
+        <v>3456400</v>
       </c>
       <c r="F46" s="3">
-        <v>3208900</v>
+        <v>3571000</v>
       </c>
       <c r="G46" s="3">
-        <v>2742200</v>
+        <v>3051700</v>
       </c>
       <c r="H46" s="3">
-        <v>2463800</v>
+        <v>2741900</v>
       </c>
       <c r="I46" s="3">
-        <v>2682900</v>
+        <v>2985600</v>
       </c>
       <c r="J46" s="3">
-        <v>2655300</v>
+        <v>2955000</v>
       </c>
       <c r="K46" s="3">
         <v>2577400</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>842400</v>
+        <v>937500</v>
       </c>
       <c r="E47" s="3">
-        <v>1555600</v>
+        <v>1721400</v>
       </c>
       <c r="F47" s="3">
-        <v>778000</v>
+        <v>865800</v>
       </c>
       <c r="G47" s="3">
-        <v>699500</v>
+        <v>778400</v>
       </c>
       <c r="H47" s="3">
-        <v>678400</v>
+        <v>755000</v>
       </c>
       <c r="I47" s="3">
-        <v>792500</v>
+        <v>881900</v>
       </c>
       <c r="J47" s="3">
-        <v>874900</v>
+        <v>973600</v>
       </c>
       <c r="K47" s="3">
         <v>883300</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1777700</v>
+        <v>1978300</v>
       </c>
       <c r="E48" s="3">
-        <v>2020100</v>
+        <v>2248000</v>
       </c>
       <c r="F48" s="3">
-        <v>1659800</v>
+        <v>1847200</v>
       </c>
       <c r="G48" s="3">
-        <v>1574200</v>
+        <v>1751900</v>
       </c>
       <c r="H48" s="3">
-        <v>1621900</v>
+        <v>1805000</v>
       </c>
       <c r="I48" s="3">
-        <v>1463300</v>
+        <v>1628500</v>
       </c>
       <c r="J48" s="3">
-        <v>1537700</v>
+        <v>1711200</v>
       </c>
       <c r="K48" s="3">
         <v>1385000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>129400</v>
+        <v>144000</v>
       </c>
       <c r="E49" s="3">
-        <v>129100</v>
+        <v>143700</v>
       </c>
       <c r="F49" s="3">
-        <v>130900</v>
+        <v>145700</v>
       </c>
       <c r="G49" s="3">
-        <v>129200</v>
+        <v>143800</v>
       </c>
       <c r="H49" s="3">
-        <v>102700</v>
+        <v>114300</v>
       </c>
       <c r="I49" s="3">
-        <v>77900</v>
+        <v>86600</v>
       </c>
       <c r="J49" s="3">
-        <v>72100</v>
+        <v>80300</v>
       </c>
       <c r="K49" s="3">
         <v>65700</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>231400</v>
+        <v>257500</v>
       </c>
       <c r="E52" s="3">
-        <v>245500</v>
+        <v>243000</v>
       </c>
       <c r="F52" s="3">
-        <v>193300</v>
+        <v>215100</v>
       </c>
       <c r="G52" s="3">
-        <v>163300</v>
+        <v>181800</v>
       </c>
       <c r="H52" s="3">
-        <v>202800</v>
+        <v>225700</v>
       </c>
       <c r="I52" s="3">
-        <v>202400</v>
+        <v>225300</v>
       </c>
       <c r="J52" s="3">
-        <v>212800</v>
+        <v>236800</v>
       </c>
       <c r="K52" s="3">
         <v>144500</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6284300</v>
+        <v>6993500</v>
       </c>
       <c r="E54" s="3">
-        <v>5955500</v>
+        <v>6627600</v>
       </c>
       <c r="F54" s="3">
-        <v>5970900</v>
+        <v>6644700</v>
       </c>
       <c r="G54" s="3">
-        <v>5308400</v>
+        <v>5907500</v>
       </c>
       <c r="H54" s="3">
-        <v>5069700</v>
+        <v>5641800</v>
       </c>
       <c r="I54" s="3">
-        <v>5219000</v>
+        <v>5807900</v>
       </c>
       <c r="J54" s="3">
-        <v>5159100</v>
+        <v>5741300</v>
       </c>
       <c r="K54" s="3">
         <v>5055800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>821600</v>
+        <v>914300</v>
       </c>
       <c r="E57" s="3">
-        <v>800100</v>
+        <v>890400</v>
       </c>
       <c r="F57" s="3">
-        <v>816600</v>
+        <v>908700</v>
       </c>
       <c r="G57" s="3">
-        <v>736900</v>
+        <v>820100</v>
       </c>
       <c r="H57" s="3">
-        <v>711900</v>
+        <v>792300</v>
       </c>
       <c r="I57" s="3">
-        <v>838500</v>
+        <v>933100</v>
       </c>
       <c r="J57" s="3">
-        <v>793600</v>
+        <v>883100</v>
       </c>
       <c r="K57" s="3">
         <v>728500</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1102900</v>
+        <v>1251300</v>
       </c>
       <c r="E58" s="3">
-        <v>1998200</v>
+        <v>2223700</v>
       </c>
       <c r="F58" s="3">
-        <v>1088100</v>
+        <v>1210900</v>
       </c>
       <c r="G58" s="3">
-        <v>861500</v>
+        <v>958800</v>
       </c>
       <c r="H58" s="3">
-        <v>810700</v>
+        <v>902200</v>
       </c>
       <c r="I58" s="3">
-        <v>680800</v>
+        <v>757600</v>
       </c>
       <c r="J58" s="3">
-        <v>741900</v>
+        <v>825600</v>
       </c>
       <c r="K58" s="3">
         <v>676100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>633200</v>
+        <v>680700</v>
       </c>
       <c r="E59" s="3">
-        <v>1040300</v>
+        <v>1157700</v>
       </c>
       <c r="F59" s="3">
-        <v>517900</v>
+        <v>576300</v>
       </c>
       <c r="G59" s="3">
-        <v>412600</v>
+        <v>459100</v>
       </c>
       <c r="H59" s="3">
-        <v>516700</v>
+        <v>575000</v>
       </c>
       <c r="I59" s="3">
-        <v>596500</v>
+        <v>663800</v>
       </c>
       <c r="J59" s="3">
-        <v>572100</v>
+        <v>636700</v>
       </c>
       <c r="K59" s="3">
         <v>572700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2557700</v>
+        <v>2846300</v>
       </c>
       <c r="E60" s="3">
-        <v>2430900</v>
+        <v>2705300</v>
       </c>
       <c r="F60" s="3">
-        <v>2422600</v>
+        <v>2696000</v>
       </c>
       <c r="G60" s="3">
-        <v>2011000</v>
+        <v>2237900</v>
       </c>
       <c r="H60" s="3">
-        <v>2039300</v>
+        <v>2269500</v>
       </c>
       <c r="I60" s="3">
-        <v>2115700</v>
+        <v>2354500</v>
       </c>
       <c r="J60" s="3">
-        <v>2107500</v>
+        <v>2345400</v>
       </c>
       <c r="K60" s="3">
         <v>1977300</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1101700</v>
+        <v>1226100</v>
       </c>
       <c r="E61" s="3">
-        <v>986000</v>
+        <v>1186400</v>
       </c>
       <c r="F61" s="3">
-        <v>1152900</v>
+        <v>1283100</v>
       </c>
       <c r="G61" s="3">
-        <v>1041100</v>
+        <v>1158600</v>
       </c>
       <c r="H61" s="3">
-        <v>842400</v>
+        <v>937400</v>
       </c>
       <c r="I61" s="3">
-        <v>888700</v>
+        <v>989000</v>
       </c>
       <c r="J61" s="3">
-        <v>907400</v>
+        <v>1009800</v>
       </c>
       <c r="K61" s="3">
         <v>1026100</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>340600</v>
+        <v>379100</v>
       </c>
       <c r="E62" s="3">
-        <v>481200</v>
+        <v>446400</v>
       </c>
       <c r="F62" s="3">
-        <v>391600</v>
+        <v>435800</v>
       </c>
       <c r="G62" s="3">
-        <v>395800</v>
+        <v>440500</v>
       </c>
       <c r="H62" s="3">
-        <v>446000</v>
+        <v>496300</v>
       </c>
       <c r="I62" s="3">
-        <v>428700</v>
+        <v>477100</v>
       </c>
       <c r="J62" s="3">
-        <v>469000</v>
+        <v>522000</v>
       </c>
       <c r="K62" s="3">
         <v>454800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4190900</v>
+        <v>4663900</v>
       </c>
       <c r="E66" s="3">
-        <v>4031000</v>
+        <v>4485900</v>
       </c>
       <c r="F66" s="3">
-        <v>4189500</v>
+        <v>4662300</v>
       </c>
       <c r="G66" s="3">
-        <v>3650500</v>
+        <v>4062400</v>
       </c>
       <c r="H66" s="3">
-        <v>3536700</v>
+        <v>3935800</v>
       </c>
       <c r="I66" s="3">
-        <v>3638900</v>
+        <v>4049600</v>
       </c>
       <c r="J66" s="3">
-        <v>3650100</v>
+        <v>4062000</v>
       </c>
       <c r="K66" s="3">
         <v>3662600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1230400</v>
+        <v>1369300</v>
       </c>
       <c r="E72" s="3">
-        <v>1223400</v>
+        <v>1361500</v>
       </c>
       <c r="F72" s="3">
-        <v>1112300</v>
+        <v>1237900</v>
       </c>
       <c r="G72" s="3">
-        <v>1075300</v>
+        <v>1196600</v>
       </c>
       <c r="H72" s="3">
-        <v>1053300</v>
+        <v>1172200</v>
       </c>
       <c r="I72" s="3">
-        <v>968100</v>
+        <v>1077400</v>
       </c>
       <c r="J72" s="3">
-        <v>817500</v>
+        <v>909700</v>
       </c>
       <c r="K72" s="3">
         <v>700600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2093400</v>
+        <v>2329700</v>
       </c>
       <c r="E76" s="3">
-        <v>1924500</v>
+        <v>2141700</v>
       </c>
       <c r="F76" s="3">
-        <v>1781400</v>
+        <v>1982500</v>
       </c>
       <c r="G76" s="3">
-        <v>1658000</v>
+        <v>1845100</v>
       </c>
       <c r="H76" s="3">
-        <v>1533000</v>
+        <v>1706000</v>
       </c>
       <c r="I76" s="3">
-        <v>1580100</v>
+        <v>1758400</v>
       </c>
       <c r="J76" s="3">
-        <v>1509000</v>
+        <v>1679300</v>
       </c>
       <c r="K76" s="3">
         <v>1393200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>41500</v>
+        <v>46200</v>
       </c>
       <c r="E81" s="3">
-        <v>101400</v>
+        <v>112800</v>
       </c>
       <c r="F81" s="3">
-        <v>64400</v>
+        <v>71700</v>
       </c>
       <c r="G81" s="3">
-        <v>63800</v>
+        <v>71000</v>
       </c>
       <c r="H81" s="3">
-        <v>112500</v>
+        <v>125200</v>
       </c>
       <c r="I81" s="3">
-        <v>185700</v>
+        <v>206700</v>
       </c>
       <c r="J81" s="3">
-        <v>182100</v>
+        <v>202700</v>
       </c>
       <c r="K81" s="3">
         <v>118400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>248500</v>
+        <v>276600</v>
       </c>
       <c r="E83" s="3">
-        <v>249400</v>
+        <v>277600</v>
       </c>
       <c r="F83" s="3">
-        <v>215100</v>
+        <v>239400</v>
       </c>
       <c r="G83" s="3">
-        <v>205200</v>
+        <v>228400</v>
       </c>
       <c r="H83" s="3">
-        <v>187700</v>
+        <v>208900</v>
       </c>
       <c r="I83" s="3">
-        <v>167600</v>
+        <v>186500</v>
       </c>
       <c r="J83" s="3">
-        <v>160200</v>
+        <v>178300</v>
       </c>
       <c r="K83" s="3">
         <v>157500</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>205700</v>
+        <v>228900</v>
       </c>
       <c r="E89" s="3">
-        <v>240600</v>
+        <v>267800</v>
       </c>
       <c r="F89" s="3">
-        <v>-80900</v>
+        <v>-90100</v>
       </c>
       <c r="G89" s="3">
-        <v>-3200</v>
+        <v>-3600</v>
       </c>
       <c r="H89" s="3">
-        <v>270700</v>
+        <v>301300</v>
       </c>
       <c r="I89" s="3">
-        <v>297800</v>
+        <v>331400</v>
       </c>
       <c r="J89" s="3">
-        <v>247800</v>
+        <v>275700</v>
       </c>
       <c r="K89" s="3">
         <v>280000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-232400</v>
+        <v>-258600</v>
       </c>
       <c r="E91" s="3">
-        <v>-228900</v>
+        <v>-254700</v>
       </c>
       <c r="F91" s="3">
-        <v>-232800</v>
+        <v>-259100</v>
       </c>
       <c r="G91" s="3">
-        <v>-213000</v>
+        <v>-237000</v>
       </c>
       <c r="H91" s="3">
-        <v>-301900</v>
+        <v>-335900</v>
       </c>
       <c r="I91" s="3">
-        <v>-274700</v>
+        <v>-305700</v>
       </c>
       <c r="J91" s="3">
-        <v>-219100</v>
+        <v>-243900</v>
       </c>
       <c r="K91" s="3">
         <v>-191700</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-158200</v>
+        <v>-176000</v>
       </c>
       <c r="E94" s="3">
-        <v>-138300</v>
+        <v>-153900</v>
       </c>
       <c r="F94" s="3">
-        <v>-255700</v>
+        <v>-284500</v>
       </c>
       <c r="G94" s="3">
-        <v>-12200</v>
+        <v>-13500</v>
       </c>
       <c r="H94" s="3">
-        <v>-211300</v>
+        <v>-235100</v>
       </c>
       <c r="I94" s="3">
-        <v>-198000</v>
+        <v>-220400</v>
       </c>
       <c r="J94" s="3">
-        <v>-219000</v>
+        <v>-243700</v>
       </c>
       <c r="K94" s="3">
         <v>-245100</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-36000</v>
+        <v>-40000</v>
       </c>
       <c r="E96" s="3">
-        <v>-27000</v>
+        <v>-30100</v>
       </c>
       <c r="F96" s="3">
-        <v>-27100</v>
+        <v>-30100</v>
       </c>
       <c r="G96" s="3">
-        <v>-38300</v>
+        <v>-42600</v>
       </c>
       <c r="H96" s="3">
-        <v>-38300</v>
+        <v>-42600</v>
       </c>
       <c r="I96" s="3">
-        <v>-36000</v>
+        <v>-40100</v>
       </c>
       <c r="J96" s="3">
-        <v>-24800</v>
+        <v>-27600</v>
       </c>
       <c r="K96" s="3">
         <v>-19000</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-59500</v>
+        <v>-66200</v>
       </c>
       <c r="E100" s="3">
-        <v>-220000</v>
+        <v>-244800</v>
       </c>
       <c r="F100" s="3">
-        <v>223400</v>
+        <v>248600</v>
       </c>
       <c r="G100" s="3">
-        <v>224200</v>
+        <v>249500</v>
       </c>
       <c r="H100" s="3">
-        <v>-1100</v>
+        <v>-1200</v>
       </c>
       <c r="I100" s="3">
-        <v>-123900</v>
+        <v>-137800</v>
       </c>
       <c r="J100" s="3">
-        <v>-12400</v>
+        <v>-13800</v>
       </c>
       <c r="K100" s="3">
         <v>-69900</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>19300</v>
+        <v>21400</v>
       </c>
       <c r="E101" s="3">
-        <v>17500</v>
+        <v>19500</v>
       </c>
       <c r="F101" s="3">
-        <v>-11600</v>
+        <v>-12900</v>
       </c>
       <c r="G101" s="3">
-        <v>-3800</v>
+        <v>-4200</v>
       </c>
       <c r="H101" s="3">
-        <v>-5900</v>
+        <v>-6600</v>
       </c>
       <c r="I101" s="3">
-        <v>5400</v>
+        <v>6100</v>
       </c>
       <c r="J101" s="3">
-        <v>6600</v>
+        <v>7400</v>
       </c>
       <c r="K101" s="3">
         <v>-2100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>7300</v>
+        <v>8100</v>
       </c>
       <c r="E102" s="3">
-        <v>-100100</v>
+        <v>-111300</v>
       </c>
       <c r="F102" s="3">
-        <v>-124800</v>
+        <v>-138800</v>
       </c>
       <c r="G102" s="3">
-        <v>205000</v>
+        <v>228200</v>
       </c>
       <c r="H102" s="3">
-        <v>52400</v>
+        <v>58300</v>
       </c>
       <c r="I102" s="3">
-        <v>-18600</v>
+        <v>-20700</v>
       </c>
       <c r="J102" s="3">
-        <v>23000</v>
+        <v>25600</v>
       </c>
       <c r="K102" s="3">
         <v>-37100</v>

--- a/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7501300</v>
+        <v>6985100</v>
       </c>
       <c r="E8" s="3">
-        <v>7570900</v>
+        <v>8021500</v>
       </c>
       <c r="F8" s="3">
-        <v>6606500</v>
+        <v>7662600</v>
       </c>
       <c r="G8" s="3">
-        <v>5762400</v>
+        <v>7338200</v>
       </c>
       <c r="H8" s="3">
-        <v>6492500</v>
+        <v>8498300</v>
       </c>
       <c r="I8" s="3">
-        <v>7040300</v>
+        <v>8948600</v>
       </c>
       <c r="J8" s="3">
-        <v>6868100</v>
+        <v>9108200</v>
       </c>
       <c r="K8" s="3">
         <v>5684100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6372500</v>
+        <v>5933900</v>
       </c>
       <c r="E9" s="3">
-        <v>6458300</v>
+        <v>6842700</v>
       </c>
       <c r="F9" s="3">
-        <v>5621800</v>
+        <v>6520400</v>
       </c>
       <c r="G9" s="3">
-        <v>4844200</v>
+        <v>6169000</v>
       </c>
       <c r="H9" s="3">
-        <v>5425800</v>
+        <v>7102100</v>
       </c>
       <c r="I9" s="3">
-        <v>5853800</v>
+        <v>7440500</v>
       </c>
       <c r="J9" s="3">
-        <v>5690000</v>
+        <v>7545900</v>
       </c>
       <c r="K9" s="3">
         <v>4644900</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1128900</v>
+        <v>1051200</v>
       </c>
       <c r="E10" s="3">
-        <v>1112600</v>
+        <v>1178800</v>
       </c>
       <c r="F10" s="3">
-        <v>984700</v>
+        <v>1142100</v>
       </c>
       <c r="G10" s="3">
-        <v>918100</v>
+        <v>1169200</v>
       </c>
       <c r="H10" s="3">
-        <v>1066700</v>
+        <v>1396200</v>
       </c>
       <c r="I10" s="3">
-        <v>1186500</v>
+        <v>1508100</v>
       </c>
       <c r="J10" s="3">
-        <v>1178000</v>
+        <v>1562300</v>
       </c>
       <c r="K10" s="3">
         <v>1039200</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>148800</v>
+        <v>138500</v>
       </c>
       <c r="E12" s="3">
-        <v>137100</v>
+        <v>145200</v>
       </c>
       <c r="F12" s="3">
-        <v>122200</v>
+        <v>141700</v>
       </c>
       <c r="G12" s="3">
-        <v>116000</v>
+        <v>147700</v>
       </c>
       <c r="H12" s="3">
-        <v>122000</v>
+        <v>159700</v>
       </c>
       <c r="I12" s="3">
-        <v>122500</v>
+        <v>155700</v>
       </c>
       <c r="J12" s="3">
-        <v>110100</v>
+        <v>146000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>4300</v>
+        <v>-64800</v>
       </c>
       <c r="E14" s="3">
-        <v>61200</v>
+        <v>-80200</v>
       </c>
       <c r="F14" s="3">
-        <v>12500</v>
+        <v>-6900</v>
       </c>
       <c r="G14" s="3">
-        <v>74300</v>
+        <v>-135300</v>
       </c>
       <c r="H14" s="3">
-        <v>32400</v>
+        <v>-74200</v>
       </c>
       <c r="I14" s="3">
-        <v>65800</v>
+        <v>30000</v>
       </c>
       <c r="J14" s="3">
-        <v>105300</v>
+        <v>60700</v>
       </c>
       <c r="K14" s="3">
         <v>91200</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>38500</v>
+        <v>35800</v>
       </c>
       <c r="E15" s="3">
-        <v>36700</v>
+        <v>38900</v>
       </c>
       <c r="F15" s="3">
-        <v>26800</v>
+        <v>31100</v>
       </c>
       <c r="G15" s="3">
-        <v>30500</v>
+        <v>38900</v>
       </c>
       <c r="H15" s="3">
-        <v>23900</v>
+        <v>31200</v>
       </c>
       <c r="I15" s="3">
-        <v>18900</v>
+        <v>24100</v>
       </c>
       <c r="J15" s="3">
-        <v>18400</v>
+        <v>24400</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7426400</v>
+        <v>6911200</v>
       </c>
       <c r="E17" s="3">
-        <v>7493900</v>
+        <v>7905300</v>
       </c>
       <c r="F17" s="3">
-        <v>6537900</v>
+        <v>7568400</v>
       </c>
       <c r="G17" s="3">
-        <v>5776800</v>
+        <v>7262000</v>
       </c>
       <c r="H17" s="3">
-        <v>6357600</v>
+        <v>8279300</v>
       </c>
       <c r="I17" s="3">
-        <v>6816100</v>
+        <v>8580000</v>
       </c>
       <c r="J17" s="3">
-        <v>6655300</v>
+        <v>8686300</v>
       </c>
       <c r="K17" s="3">
         <v>5515000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>75000</v>
+        <v>73900</v>
       </c>
       <c r="E18" s="3">
-        <v>77100</v>
+        <v>116200</v>
       </c>
       <c r="F18" s="3">
-        <v>68600</v>
+        <v>94100</v>
       </c>
       <c r="G18" s="3">
-        <v>-14500</v>
+        <v>76200</v>
       </c>
       <c r="H18" s="3">
-        <v>134900</v>
+        <v>219000</v>
       </c>
       <c r="I18" s="3">
-        <v>224100</v>
+        <v>368600</v>
       </c>
       <c r="J18" s="3">
-        <v>212800</v>
+        <v>421900</v>
       </c>
       <c r="K18" s="3">
         <v>169100</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>133100</v>
+        <v>-35100</v>
       </c>
       <c r="E20" s="3">
-        <v>166100</v>
+        <v>-60300</v>
       </c>
       <c r="F20" s="3">
-        <v>100400</v>
+        <v>-77200</v>
       </c>
       <c r="G20" s="3">
-        <v>191300</v>
+        <v>7200</v>
       </c>
       <c r="H20" s="3">
-        <v>114100</v>
+        <v>-8200</v>
       </c>
       <c r="I20" s="3">
-        <v>58700</v>
+        <v>9600</v>
       </c>
       <c r="J20" s="3">
-        <v>102800</v>
+        <v>-33100</v>
       </c>
       <c r="K20" s="3">
         <v>42800</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>482600</v>
+        <v>144800</v>
       </c>
       <c r="E21" s="3">
-        <v>518900</v>
+        <v>215300</v>
       </c>
       <c r="F21" s="3">
-        <v>406700</v>
+        <v>202400</v>
       </c>
       <c r="G21" s="3">
-        <v>403600</v>
+        <v>108000</v>
       </c>
       <c r="H21" s="3">
-        <v>456500</v>
+        <v>258400</v>
       </c>
       <c r="I21" s="3">
-        <v>468000</v>
+        <v>383000</v>
       </c>
       <c r="J21" s="3">
-        <v>492500</v>
+        <v>479400</v>
       </c>
       <c r="K21" s="3">
         <v>370200</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>65600</v>
+        <v>61100</v>
       </c>
       <c r="E22" s="3">
-        <v>45000</v>
+        <v>47600</v>
       </c>
       <c r="F22" s="3">
-        <v>24000</v>
+        <v>27800</v>
       </c>
       <c r="G22" s="3">
-        <v>25500</v>
+        <v>32400</v>
       </c>
       <c r="H22" s="3">
-        <v>30700</v>
+        <v>40200</v>
       </c>
       <c r="I22" s="3">
-        <v>28900</v>
+        <v>36800</v>
       </c>
       <c r="J22" s="3">
-        <v>28200</v>
+        <v>37400</v>
       </c>
       <c r="K22" s="3">
         <v>23500</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>142500</v>
+        <v>132600</v>
       </c>
       <c r="E23" s="3">
-        <v>198200</v>
+        <v>227900</v>
       </c>
       <c r="F23" s="3">
-        <v>145100</v>
+        <v>168200</v>
       </c>
       <c r="G23" s="3">
-        <v>151300</v>
+        <v>192700</v>
       </c>
       <c r="H23" s="3">
-        <v>218300</v>
+        <v>285800</v>
       </c>
       <c r="I23" s="3">
-        <v>253900</v>
+        <v>322700</v>
       </c>
       <c r="J23" s="3">
-        <v>287300</v>
+        <v>381000</v>
       </c>
       <c r="K23" s="3">
         <v>188500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>82300</v>
+        <v>76600</v>
       </c>
       <c r="E24" s="3">
-        <v>73100</v>
+        <v>80100</v>
       </c>
       <c r="F24" s="3">
-        <v>51000</v>
+        <v>59200</v>
       </c>
       <c r="G24" s="3">
-        <v>65500</v>
+        <v>83400</v>
       </c>
       <c r="H24" s="3">
-        <v>83500</v>
+        <v>109200</v>
       </c>
       <c r="I24" s="3">
-        <v>23500</v>
+        <v>29900</v>
       </c>
       <c r="J24" s="3">
-        <v>57900</v>
+        <v>76700</v>
       </c>
       <c r="K24" s="3">
         <v>37300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>60200</v>
+        <v>56000</v>
       </c>
       <c r="E26" s="3">
-        <v>125200</v>
+        <v>147800</v>
       </c>
       <c r="F26" s="3">
-        <v>94000</v>
+        <v>109000</v>
       </c>
       <c r="G26" s="3">
-        <v>85900</v>
+        <v>109400</v>
       </c>
       <c r="H26" s="3">
-        <v>134900</v>
+        <v>176500</v>
       </c>
       <c r="I26" s="3">
-        <v>230400</v>
+        <v>292800</v>
       </c>
       <c r="J26" s="3">
-        <v>229400</v>
+        <v>304300</v>
       </c>
       <c r="K26" s="3">
         <v>151200</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>46200</v>
+        <v>43000</v>
       </c>
       <c r="E27" s="3">
-        <v>112800</v>
+        <v>134700</v>
       </c>
       <c r="F27" s="3">
-        <v>71700</v>
+        <v>83100</v>
       </c>
       <c r="G27" s="3">
-        <v>71000</v>
+        <v>90400</v>
       </c>
       <c r="H27" s="3">
-        <v>125200</v>
+        <v>163900</v>
       </c>
       <c r="I27" s="3">
-        <v>206700</v>
+        <v>262700</v>
       </c>
       <c r="J27" s="3">
-        <v>202700</v>
+        <v>268800</v>
       </c>
       <c r="K27" s="3">
         <v>118400</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-133100</v>
+        <v>35100</v>
       </c>
       <c r="E32" s="3">
-        <v>-166100</v>
+        <v>60300</v>
       </c>
       <c r="F32" s="3">
-        <v>-100400</v>
+        <v>77200</v>
       </c>
       <c r="G32" s="3">
-        <v>-191300</v>
+        <v>-7200</v>
       </c>
       <c r="H32" s="3">
-        <v>-114100</v>
+        <v>8200</v>
       </c>
       <c r="I32" s="3">
-        <v>-58700</v>
+        <v>-9600</v>
       </c>
       <c r="J32" s="3">
-        <v>-102800</v>
+        <v>33100</v>
       </c>
       <c r="K32" s="3">
         <v>-42800</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>46200</v>
+        <v>43000</v>
       </c>
       <c r="E33" s="3">
-        <v>112800</v>
+        <v>134700</v>
       </c>
       <c r="F33" s="3">
-        <v>71700</v>
+        <v>83100</v>
       </c>
       <c r="G33" s="3">
-        <v>71000</v>
+        <v>90400</v>
       </c>
       <c r="H33" s="3">
-        <v>125200</v>
+        <v>163900</v>
       </c>
       <c r="I33" s="3">
-        <v>206700</v>
+        <v>262700</v>
       </c>
       <c r="J33" s="3">
-        <v>202700</v>
+        <v>268800</v>
       </c>
       <c r="K33" s="3">
         <v>118400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>46200</v>
+        <v>43000</v>
       </c>
       <c r="E35" s="3">
-        <v>112800</v>
+        <v>134700</v>
       </c>
       <c r="F35" s="3">
-        <v>71700</v>
+        <v>83100</v>
       </c>
       <c r="G35" s="3">
-        <v>71000</v>
+        <v>90400</v>
       </c>
       <c r="H35" s="3">
-        <v>125200</v>
+        <v>163900</v>
       </c>
       <c r="I35" s="3">
-        <v>206700</v>
+        <v>262700</v>
       </c>
       <c r="J35" s="3">
-        <v>202700</v>
+        <v>268800</v>
       </c>
       <c r="K35" s="3">
         <v>118400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>347200</v>
+        <v>323300</v>
       </c>
       <c r="E41" s="3">
-        <v>336800</v>
+        <v>356800</v>
       </c>
       <c r="F41" s="3">
-        <v>462600</v>
+        <v>536500</v>
       </c>
       <c r="G41" s="3">
-        <v>599000</v>
+        <v>762800</v>
       </c>
       <c r="H41" s="3">
-        <v>385900</v>
+        <v>505200</v>
       </c>
       <c r="I41" s="3">
-        <v>316900</v>
+        <v>402700</v>
       </c>
       <c r="J41" s="3">
-        <v>359500</v>
+        <v>476800</v>
       </c>
       <c r="K41" s="3">
         <v>317900</v>
@@ -2038,22 +2038,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33700</v>
+        <v>31400</v>
       </c>
       <c r="E42" s="3">
-        <v>36400</v>
+        <v>38600</v>
       </c>
       <c r="F42" s="3">
-        <v>23100</v>
+        <v>26800</v>
       </c>
       <c r="G42" s="3">
-        <v>20800</v>
+        <v>26400</v>
       </c>
       <c r="H42" s="3">
-        <v>6400</v>
+        <v>8400</v>
       </c>
       <c r="I42" s="3">
-        <v>16800</v>
+        <v>21400</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1736000</v>
+        <v>1616500</v>
       </c>
       <c r="E43" s="3">
-        <v>1619900</v>
+        <v>1716300</v>
       </c>
       <c r="F43" s="3">
-        <v>1627900</v>
+        <v>1888100</v>
       </c>
       <c r="G43" s="3">
-        <v>1356400</v>
+        <v>1727300</v>
       </c>
       <c r="H43" s="3">
-        <v>1357900</v>
+        <v>1777500</v>
       </c>
       <c r="I43" s="3">
-        <v>1549600</v>
+        <v>1969700</v>
       </c>
       <c r="J43" s="3">
-        <v>1584200</v>
+        <v>2100800</v>
       </c>
       <c r="K43" s="3">
         <v>1332000</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1303900</v>
+        <v>1214100</v>
       </c>
       <c r="E44" s="3">
-        <v>1223300</v>
+        <v>1296100</v>
       </c>
       <c r="F44" s="3">
-        <v>1165200</v>
+        <v>1351500</v>
       </c>
       <c r="G44" s="3">
-        <v>857900</v>
+        <v>1092600</v>
       </c>
       <c r="H44" s="3">
-        <v>822600</v>
+        <v>1076800</v>
       </c>
       <c r="I44" s="3">
-        <v>872500</v>
+        <v>1109000</v>
       </c>
       <c r="J44" s="3">
-        <v>807900</v>
+        <v>1071400</v>
       </c>
       <c r="K44" s="3">
         <v>703300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>255400</v>
+        <v>237900</v>
       </c>
       <c r="E45" s="3">
-        <v>240000</v>
+        <v>254300</v>
       </c>
       <c r="F45" s="3">
-        <v>292200</v>
+        <v>338900</v>
       </c>
       <c r="G45" s="3">
-        <v>217700</v>
+        <v>277200</v>
       </c>
       <c r="H45" s="3">
-        <v>169000</v>
+        <v>221200</v>
       </c>
       <c r="I45" s="3">
-        <v>229800</v>
+        <v>292100</v>
       </c>
       <c r="J45" s="3">
-        <v>273900</v>
+        <v>269700</v>
       </c>
       <c r="K45" s="3">
         <v>223700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3676100</v>
+        <v>3423100</v>
       </c>
       <c r="E46" s="3">
-        <v>3456400</v>
+        <v>3662100</v>
       </c>
       <c r="F46" s="3">
-        <v>3571000</v>
+        <v>4141900</v>
       </c>
       <c r="G46" s="3">
-        <v>3051700</v>
+        <v>3886200</v>
       </c>
       <c r="H46" s="3">
-        <v>2741900</v>
+        <v>3589000</v>
       </c>
       <c r="I46" s="3">
-        <v>2985600</v>
+        <v>3794900</v>
       </c>
       <c r="J46" s="3">
-        <v>2955000</v>
+        <v>4012300</v>
       </c>
       <c r="K46" s="3">
         <v>2577400</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>937500</v>
+        <v>1056200</v>
       </c>
       <c r="E47" s="3">
-        <v>1721400</v>
+        <v>1121300</v>
       </c>
       <c r="F47" s="3">
-        <v>865800</v>
+        <v>1188500</v>
       </c>
       <c r="G47" s="3">
-        <v>778400</v>
+        <v>1159900</v>
       </c>
       <c r="H47" s="3">
-        <v>755000</v>
+        <v>1146800</v>
       </c>
       <c r="I47" s="3">
-        <v>881900</v>
+        <v>1284200</v>
       </c>
       <c r="J47" s="3">
-        <v>973600</v>
+        <v>1488100</v>
       </c>
       <c r="K47" s="3">
         <v>883300</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1978300</v>
+        <v>1842200</v>
       </c>
       <c r="E48" s="3">
-        <v>2248000</v>
+        <v>2025700</v>
       </c>
       <c r="F48" s="3">
-        <v>1847200</v>
+        <v>2142400</v>
       </c>
       <c r="G48" s="3">
-        <v>1751900</v>
+        <v>2231000</v>
       </c>
       <c r="H48" s="3">
-        <v>1805000</v>
+        <v>2362600</v>
       </c>
       <c r="I48" s="3">
-        <v>1628500</v>
+        <v>2069800</v>
       </c>
       <c r="J48" s="3">
-        <v>1711200</v>
+        <v>2040700</v>
       </c>
       <c r="K48" s="3">
         <v>1385000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>144000</v>
+        <v>134100</v>
       </c>
       <c r="E49" s="3">
-        <v>143700</v>
+        <v>152200</v>
       </c>
       <c r="F49" s="3">
-        <v>145700</v>
+        <v>169000</v>
       </c>
       <c r="G49" s="3">
-        <v>143800</v>
+        <v>183100</v>
       </c>
       <c r="H49" s="3">
-        <v>114300</v>
+        <v>149600</v>
       </c>
       <c r="I49" s="3">
-        <v>86600</v>
+        <v>110100</v>
       </c>
       <c r="J49" s="3">
-        <v>80300</v>
+        <v>106400</v>
       </c>
       <c r="K49" s="3">
         <v>65700</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>257500</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>243000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>215100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>181800</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>225700</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>225300</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>236800</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>144500</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6993500</v>
+        <v>6512200</v>
       </c>
       <c r="E54" s="3">
-        <v>6627600</v>
+        <v>7032300</v>
       </c>
       <c r="F54" s="3">
-        <v>6644700</v>
+        <v>7706900</v>
       </c>
       <c r="G54" s="3">
-        <v>5907500</v>
+        <v>7523100</v>
       </c>
       <c r="H54" s="3">
-        <v>5641800</v>
+        <v>7384800</v>
       </c>
       <c r="I54" s="3">
-        <v>5807900</v>
+        <v>7382200</v>
       </c>
       <c r="J54" s="3">
-        <v>5741300</v>
+        <v>7681600</v>
       </c>
       <c r="K54" s="3">
         <v>5055800</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>914300</v>
+        <v>851400</v>
       </c>
       <c r="E57" s="3">
-        <v>890400</v>
+        <v>943400</v>
       </c>
       <c r="F57" s="3">
-        <v>908700</v>
+        <v>1054000</v>
       </c>
       <c r="G57" s="3">
-        <v>820100</v>
+        <v>1044300</v>
       </c>
       <c r="H57" s="3">
-        <v>792300</v>
+        <v>1037000</v>
       </c>
       <c r="I57" s="3">
-        <v>933100</v>
+        <v>1186000</v>
       </c>
       <c r="J57" s="3">
-        <v>883100</v>
+        <v>1171200</v>
       </c>
       <c r="K57" s="3">
         <v>728500</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1251300</v>
+        <v>1142900</v>
       </c>
       <c r="E58" s="3">
-        <v>2223700</v>
+        <v>1273400</v>
       </c>
       <c r="F58" s="3">
-        <v>1210900</v>
+        <v>1391700</v>
       </c>
       <c r="G58" s="3">
-        <v>958800</v>
+        <v>1207300</v>
       </c>
       <c r="H58" s="3">
-        <v>902200</v>
+        <v>1166500</v>
       </c>
       <c r="I58" s="3">
-        <v>757600</v>
+        <v>963000</v>
       </c>
       <c r="J58" s="3">
-        <v>825600</v>
+        <v>1094900</v>
       </c>
       <c r="K58" s="3">
         <v>676100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>680700</v>
+        <v>656100</v>
       </c>
       <c r="E59" s="3">
-        <v>1157700</v>
+        <v>649500</v>
       </c>
       <c r="F59" s="3">
-        <v>576300</v>
+        <v>681300</v>
       </c>
       <c r="G59" s="3">
-        <v>459100</v>
+        <v>598400</v>
       </c>
       <c r="H59" s="3">
-        <v>575000</v>
+        <v>767100</v>
       </c>
       <c r="I59" s="3">
-        <v>663800</v>
+        <v>843700</v>
       </c>
       <c r="J59" s="3">
-        <v>636700</v>
+        <v>844300</v>
       </c>
       <c r="K59" s="3">
         <v>572700</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2846300</v>
+        <v>2650500</v>
       </c>
       <c r="E60" s="3">
-        <v>2705300</v>
+        <v>2866300</v>
       </c>
       <c r="F60" s="3">
-        <v>2696000</v>
+        <v>3126900</v>
       </c>
       <c r="G60" s="3">
-        <v>2237900</v>
+        <v>2850000</v>
       </c>
       <c r="H60" s="3">
-        <v>2269500</v>
+        <v>2970600</v>
       </c>
       <c r="I60" s="3">
-        <v>2354500</v>
+        <v>2992700</v>
       </c>
       <c r="J60" s="3">
-        <v>2345400</v>
+        <v>3110400</v>
       </c>
       <c r="K60" s="3">
         <v>1977300</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1226100</v>
+        <v>1141700</v>
       </c>
       <c r="E61" s="3">
-        <v>1186400</v>
+        <v>1162600</v>
       </c>
       <c r="F61" s="3">
-        <v>1283100</v>
+        <v>1425600</v>
       </c>
       <c r="G61" s="3">
-        <v>1158600</v>
+        <v>1420400</v>
       </c>
       <c r="H61" s="3">
-        <v>937400</v>
+        <v>1167000</v>
       </c>
       <c r="I61" s="3">
-        <v>989000</v>
+        <v>1257100</v>
       </c>
       <c r="J61" s="3">
-        <v>1009800</v>
+        <v>1339200</v>
       </c>
       <c r="K61" s="3">
         <v>1026100</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>379100</v>
+        <v>159700</v>
       </c>
       <c r="E62" s="3">
-        <v>446400</v>
+        <v>226000</v>
       </c>
       <c r="F62" s="3">
-        <v>435800</v>
+        <v>207300</v>
       </c>
       <c r="G62" s="3">
-        <v>440500</v>
+        <v>213500</v>
       </c>
       <c r="H62" s="3">
-        <v>496300</v>
+        <v>209200</v>
       </c>
       <c r="I62" s="3">
-        <v>477100</v>
+        <v>161700</v>
       </c>
       <c r="J62" s="3">
-        <v>522000</v>
+        <v>174200</v>
       </c>
       <c r="K62" s="3">
         <v>454800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>4663900</v>
+        <v>4145100</v>
       </c>
       <c r="E66" s="3">
-        <v>4485900</v>
+        <v>4542500</v>
       </c>
       <c r="F66" s="3">
-        <v>4662300</v>
+        <v>5120600</v>
       </c>
       <c r="G66" s="3">
-        <v>4062400</v>
+        <v>4886400</v>
       </c>
       <c r="H66" s="3">
-        <v>3935800</v>
+        <v>4847400</v>
       </c>
       <c r="I66" s="3">
-        <v>4049600</v>
+        <v>4856200</v>
       </c>
       <c r="J66" s="3">
-        <v>4062000</v>
+        <v>5119800</v>
       </c>
       <c r="K66" s="3">
         <v>3662600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1369300</v>
+        <v>1275000</v>
       </c>
       <c r="E72" s="3">
-        <v>1361500</v>
+        <v>1420600</v>
       </c>
       <c r="F72" s="3">
-        <v>1237900</v>
+        <v>1435700</v>
       </c>
       <c r="G72" s="3">
-        <v>1196600</v>
+        <v>1523900</v>
       </c>
       <c r="H72" s="3">
-        <v>1172200</v>
+        <v>1534400</v>
       </c>
       <c r="I72" s="3">
-        <v>1077400</v>
+        <v>1369400</v>
       </c>
       <c r="J72" s="3">
-        <v>909700</v>
+        <v>1206400</v>
       </c>
       <c r="K72" s="3">
         <v>700600</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2329700</v>
+        <v>2169300</v>
       </c>
       <c r="E76" s="3">
-        <v>2141700</v>
+        <v>2283400</v>
       </c>
       <c r="F76" s="3">
-        <v>1982500</v>
+        <v>2299300</v>
       </c>
       <c r="G76" s="3">
-        <v>1845100</v>
+        <v>2349700</v>
       </c>
       <c r="H76" s="3">
-        <v>1706000</v>
+        <v>2233000</v>
       </c>
       <c r="I76" s="3">
-        <v>1758400</v>
+        <v>2235000</v>
       </c>
       <c r="J76" s="3">
-        <v>1679300</v>
+        <v>2227000</v>
       </c>
       <c r="K76" s="3">
         <v>1393200</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>46200</v>
+        <v>43000</v>
       </c>
       <c r="E81" s="3">
-        <v>112800</v>
+        <v>134700</v>
       </c>
       <c r="F81" s="3">
-        <v>71700</v>
+        <v>83100</v>
       </c>
       <c r="G81" s="3">
-        <v>71000</v>
+        <v>90400</v>
       </c>
       <c r="H81" s="3">
-        <v>125200</v>
+        <v>163900</v>
       </c>
       <c r="I81" s="3">
-        <v>206700</v>
+        <v>262700</v>
       </c>
       <c r="J81" s="3">
-        <v>202700</v>
+        <v>268800</v>
       </c>
       <c r="K81" s="3">
         <v>118400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>276600</v>
+        <v>257500</v>
       </c>
       <c r="E83" s="3">
-        <v>277600</v>
+        <v>294100</v>
       </c>
       <c r="F83" s="3">
-        <v>239400</v>
+        <v>277700</v>
       </c>
       <c r="G83" s="3">
-        <v>228400</v>
+        <v>290800</v>
       </c>
       <c r="H83" s="3">
-        <v>208900</v>
+        <v>273400</v>
       </c>
       <c r="I83" s="3">
-        <v>186500</v>
+        <v>237100</v>
       </c>
       <c r="J83" s="3">
-        <v>178300</v>
+        <v>236400</v>
       </c>
       <c r="K83" s="3">
         <v>157500</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>228900</v>
+        <v>210900</v>
       </c>
       <c r="E89" s="3">
-        <v>267800</v>
+        <v>274700</v>
       </c>
       <c r="F89" s="3">
-        <v>-90100</v>
+        <v>-109300</v>
       </c>
       <c r="G89" s="3">
-        <v>-3600</v>
+        <v>-4300</v>
       </c>
       <c r="H89" s="3">
-        <v>301300</v>
+        <v>389800</v>
       </c>
       <c r="I89" s="3">
-        <v>331400</v>
+        <v>419300</v>
       </c>
       <c r="J89" s="3">
-        <v>275700</v>
+        <v>361800</v>
       </c>
       <c r="K89" s="3">
         <v>280000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-258600</v>
+        <v>-240800</v>
       </c>
       <c r="E91" s="3">
-        <v>-254700</v>
+        <v>-269900</v>
       </c>
       <c r="F91" s="3">
-        <v>-259100</v>
+        <v>-300500</v>
       </c>
       <c r="G91" s="3">
-        <v>-237000</v>
+        <v>-301900</v>
       </c>
       <c r="H91" s="3">
-        <v>-335900</v>
+        <v>-439700</v>
       </c>
       <c r="I91" s="3">
-        <v>-305700</v>
+        <v>-388500</v>
       </c>
       <c r="J91" s="3">
-        <v>-243900</v>
+        <v>-323400</v>
       </c>
       <c r="K91" s="3">
         <v>-191700</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-176000</v>
+        <v>-163900</v>
       </c>
       <c r="E94" s="3">
-        <v>-153900</v>
+        <v>-163100</v>
       </c>
       <c r="F94" s="3">
-        <v>-284500</v>
+        <v>-330000</v>
       </c>
       <c r="G94" s="3">
-        <v>-13500</v>
+        <v>-17300</v>
       </c>
       <c r="H94" s="3">
-        <v>-235100</v>
+        <v>-307800</v>
       </c>
       <c r="I94" s="3">
-        <v>-220400</v>
+        <v>-280100</v>
       </c>
       <c r="J94" s="3">
-        <v>-243700</v>
+        <v>-323100</v>
       </c>
       <c r="K94" s="3">
         <v>-245100</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-40000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-30100</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-30100</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-42600</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-42600</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-40100</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-27600</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-19000</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-66200</v>
+        <v>-61600</v>
       </c>
       <c r="E100" s="3">
-        <v>-244800</v>
+        <v>-259300</v>
       </c>
       <c r="F100" s="3">
-        <v>248600</v>
+        <v>288400</v>
       </c>
       <c r="G100" s="3">
-        <v>249500</v>
+        <v>317700</v>
       </c>
       <c r="H100" s="3">
-        <v>-1200</v>
+        <v>-1600</v>
       </c>
       <c r="I100" s="3">
-        <v>-137800</v>
+        <v>-175200</v>
       </c>
       <c r="J100" s="3">
-        <v>-13800</v>
+        <v>-18300</v>
       </c>
       <c r="K100" s="3">
         <v>-69900</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>21400</v>
+        <v>20000</v>
       </c>
       <c r="E101" s="3">
-        <v>19500</v>
+        <v>20700</v>
       </c>
       <c r="F101" s="3">
-        <v>-12900</v>
+        <v>-14900</v>
       </c>
       <c r="G101" s="3">
-        <v>-4200</v>
+        <v>-5400</v>
       </c>
       <c r="H101" s="3">
-        <v>-6600</v>
+        <v>-8600</v>
       </c>
       <c r="I101" s="3">
-        <v>6100</v>
+        <v>7700</v>
       </c>
       <c r="J101" s="3">
-        <v>7400</v>
+        <v>9800</v>
       </c>
       <c r="K101" s="3">
         <v>-2100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>8100</v>
+        <v>5300</v>
       </c>
       <c r="E102" s="3">
-        <v>-111300</v>
+        <v>-127000</v>
       </c>
       <c r="F102" s="3">
-        <v>-138800</v>
+        <v>-165800</v>
       </c>
       <c r="G102" s="3">
-        <v>228200</v>
+        <v>290800</v>
       </c>
       <c r="H102" s="3">
-        <v>58300</v>
+        <v>71800</v>
       </c>
       <c r="I102" s="3">
-        <v>-20700</v>
+        <v>-28400</v>
       </c>
       <c r="J102" s="3">
-        <v>25600</v>
+        <v>30200</v>
       </c>
       <c r="K102" s="3">
         <v>-37100</v>

--- a/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8025200</v>
+      </c>
+      <c r="E8" s="3">
         <v>6985100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8021500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7662600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7338200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8498300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8948600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9108200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5684100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6430400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7402500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8535100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8405700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8306000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6678200</v>
+      </c>
+      <c r="E9" s="3">
         <v>5933900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6842700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6520400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6169000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7102100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7440500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7545900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4644900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5394500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6347100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7276800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>7152200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7114000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1051200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1178800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1142100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1169200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1396200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1508100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1562300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1039200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1035900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1055300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1258300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1253400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1192000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>138500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>145200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>141700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>147700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>159700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>155700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>146000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>119300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>130100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>148600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>133600</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,80 +979,86 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-64800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-80200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-6900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-135300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-74200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>30000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>60700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>91200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>131500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>82200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>115400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>37400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>212800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>275500</v>
+      </c>
+      <c r="E15" s="3">
         <v>35800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>31100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>38900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>31200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24400</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
@@ -1047,15 +1069,18 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
         <v>36500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>31600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7710700</v>
+      </c>
+      <c r="E17" s="3">
         <v>6911200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7905300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7568400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7262000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8279300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8580000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8686300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5515000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6362500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7332200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8417300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8281600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8374700</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>314500</v>
+      </c>
+      <c r="E18" s="3">
         <v>73900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>116200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>94100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>76200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>219000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>368600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>421900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>169100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>67800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>117800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>124100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-68700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-35100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-60300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-77200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-33100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>42800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>116600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>101700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>82400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>38600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>133500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>638900</v>
+      </c>
+      <c r="E21" s="3">
         <v>144800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>215300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>202400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>108000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>258400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>383000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>479400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>370200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>353600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>366200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>458800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>484700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>419800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E22" s="3">
         <v>61100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>47600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>32400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>36800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>37400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>27300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>34100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>41700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>46100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>47400</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>361200</v>
+      </c>
+      <c r="E23" s="3">
         <v>132600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>227900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>168200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>192700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>285800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>322700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>381000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>188500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>157100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>137900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>158500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>116600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>17500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E24" s="3">
         <v>76600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>80100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>59200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>83400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>109200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>29900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>76700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>37300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>57100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>82800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>64000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>103900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E26" s="3">
         <v>56000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>147800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>109000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>109400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>176500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>292800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>304300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>151200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>98800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>80800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>75700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>52600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-86400</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E27" s="3">
         <v>43000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>134700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>83100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>90400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>163900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>262700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>268800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>118400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>73600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>62700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>51400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100600</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E32" s="3">
         <v>35100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>60300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>77200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>33100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-42800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-116600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-101700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-82400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-38600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-133500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E33" s="3">
         <v>43000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>134700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>83100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>90400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>163900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>262700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>268800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>118400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>73600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>62700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>51400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100600</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E35" s="3">
         <v>43000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>134700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>83100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>90400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>163900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>262700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>268800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>118400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>73600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>62700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>51400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100600</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,85 +2072,89 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400500</v>
+      </c>
+      <c r="E41" s="3">
         <v>323300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>356800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>536500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>762800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>505200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>402700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>476800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>317900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>385900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>256000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>244700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>284500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E42" s="3">
         <v>31400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>38600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>21400</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100</v>
-      </c>
-      <c r="M42" s="3">
-        <v>200</v>
       </c>
       <c r="N42" s="3">
         <v>200</v>
@@ -2074,326 +2163,350 @@
         <v>200</v>
       </c>
       <c r="P42" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q42" s="3">
         <v>1000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1731700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1616500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1716300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1888100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1727300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1777500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1969700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2100800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1332000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1364300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1612800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1812600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2010800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1998800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1302500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1214100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1296100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1351500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1092600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1076800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1109000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1071400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>703300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>684800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>848200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>858000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>947600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>857800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>235700</v>
+      </c>
+      <c r="E45" s="3">
         <v>237900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>254300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>338900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>277200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>221200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>292100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>269700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>223700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>240600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>428800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>382100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>326100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>368300</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3715800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3423100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3662100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4141900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3886200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3589000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3794900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4012300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2577400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2675600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3146000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3297700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3569100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3526400</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>828000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1056200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1121300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1188500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1159900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1146800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1284200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1488100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>883300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>832500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1175900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1246200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1047700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>934400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1849900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1842200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2025700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2142400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2231000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2362600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2069800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2040700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1385000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1444600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1699300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1750200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2546000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2369600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E49" s="3">
         <v>134100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>152200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>169000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>183100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>149600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>110100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>106400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>65700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>62600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>77000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>87900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>114700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>126300</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,9 +2597,12 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2509,26 +2628,29 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>144500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>171700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>163800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>166000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>173600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>185800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6591200</v>
+      </c>
+      <c r="E54" s="3">
         <v>6512200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7032300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7706900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7523100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7384800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7382200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7681600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5055800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5187100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6262100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6548000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7451100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7142600</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>912700</v>
+      </c>
+      <c r="E57" s="3">
         <v>851400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>943400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1054000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1044300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1037000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1186000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1171200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>728500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>737900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>941700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>956100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1210100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1102900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1033700</v>
+      </c>
+      <c r="E58" s="3">
         <v>1142900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1273400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1391700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1207300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1166500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>963000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1094900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>676100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>910000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>910600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1099300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1157900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1432100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>687800</v>
+      </c>
+      <c r="E59" s="3">
         <v>656100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>649500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>681300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>598400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>767100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>843700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>844300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>572700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>552200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>597100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>636400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>612300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>590100</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2634200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2650500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2866300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3126900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2850000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2970600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2992700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3110400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1977300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2200200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2449400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2691800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2980300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3125100</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1094100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1141700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1162600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1425600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1420400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1167000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1257100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1339200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1026100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1005500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1431200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1445800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1755400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1507900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>159100</v>
+      </c>
+      <c r="E62" s="3">
         <v>159700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>226000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>207300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>213500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>209200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>161700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>174200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>454800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>521800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>549800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>580800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>689700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>723500</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4098100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4145100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4542500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5120600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4886400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4847400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4856200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5119800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3662600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3914300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4635100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4924500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5944500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5834500</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1327800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1275000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1420600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1435700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1523900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1534400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1369400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1206400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>700600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>663800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>710300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>725600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>692000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>655200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2280100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2169300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2283400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2299300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2349700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2233000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2235000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2227000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1393200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1272700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1627000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1623500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1506600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1308000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>222800</v>
+      </c>
+      <c r="E81" s="3">
         <v>43000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>134700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>83100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>90400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>163900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>262700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>268800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>118400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>73600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>62700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>51400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100600</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>275500</v>
+      </c>
+      <c r="E83" s="3">
         <v>257500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>294100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>277700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>290800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>273400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>237100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>236400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>157500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>170800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>192000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>257500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>321300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>354500</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>399600</v>
+      </c>
+      <c r="E89" s="3">
         <v>210900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>274700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-109300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>389800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>419300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>361800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>280000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>313000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>356300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>42400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>278200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-245400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-240800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-269900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-301900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-439700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-388500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-323400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-191700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-188500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-236100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-360600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-415900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-277000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-163900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-163100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-330000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-307800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-280100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-323100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-245100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>14300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-369100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-408500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-183100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4248,26 +4481,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-19000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-15500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-18000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-19400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-294800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-61600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-259300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>288400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>317700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-175200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-69900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-153900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-132500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>274000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-103600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-206500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E101" s="3">
         <v>20000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>20700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-14900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>12500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>15200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-127000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-165800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>290800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>71800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-28400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-37100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>163000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>35600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-47200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-118500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FUWAY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>FUWAY</t>
   </si>
@@ -892,8 +892,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>145100</v>
       </c>
       <c r="E12" s="3">
         <v>138500</v>
@@ -1037,7 +1037,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>275500</v>
+        <v>37400</v>
       </c>
       <c r="E15" s="3">
         <v>35800</v>
@@ -1266,7 +1266,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>638900</v>
+        <v>400800</v>
       </c>
       <c r="E21" s="3">
         <v>144800</v>
